--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7471,14 +7471,14 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
         <v>10266000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>22915</v>
+        <v>22864</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7489,7 +7489,7 @@
         <v>10266000</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>22915</v>
+        <v>22864</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -13604,38 +13604,30 @@
       </c>
       <c r="F202" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I202" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>12803000</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>26290</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K202" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L202" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K202" s="5" t="n">
+        <v>12803000</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>26290</v>
       </c>
       <c r="M202" s="3" t="inlineStr">
         <is>
@@ -13644,7 +13636,7 @@
       </c>
       <c r="N202" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15638,34 +15630,34 @@
       </c>
       <c r="F233" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
-        <v>8735000</v>
+        <v>7687000</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>27043</v>
+        <v>23799</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K233" s="5" t="n">
-        <v>7686800</v>
+        <v>7687000</v>
       </c>
       <c r="L233" s="5" t="n">
-        <v>23798</v>
+        <v>23799</v>
       </c>
       <c r="M233" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N233" s="3" t="inlineStr">
@@ -19545,7 +19537,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -24070,34 +24062,34 @@
       </c>
       <c r="F365" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
-        <v>11309000</v>
+        <v>9952000</v>
       </c>
       <c r="I365" s="5" t="n">
-        <v>24638</v>
+        <v>21682</v>
       </c>
       <c r="J365" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K365" s="5" t="n">
-        <v>9951920</v>
+        <v>9952000</v>
       </c>
       <c r="L365" s="5" t="n">
         <v>21682</v>
       </c>
       <c r="M365" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N365" s="3" t="inlineStr">
@@ -27542,7 +27534,7 @@
         </is>
       </c>
       <c r="E419" s="4" t="n">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
@@ -27558,7 +27550,7 @@
         <v>11909000</v>
       </c>
       <c r="I419" s="5" t="n">
-        <v>25447</v>
+        <v>25501</v>
       </c>
       <c r="J419" s="3" t="inlineStr">
         <is>
@@ -27569,7 +27561,7 @@
         <v>11909000</v>
       </c>
       <c r="L419" s="5" t="n">
-        <v>25447</v>
+        <v>25501</v>
       </c>
       <c r="M419" s="3" t="inlineStr">
         <is>
@@ -43080,10 +43072,10 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 448呎 (2房)
+          <t>F | 449呎 (2房)
 $1027万
-$22,915/呎
-(26年-08月-07日)</t>
+$22,864/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -43739,7 +43731,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>39</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43749,7 +43741,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43921,7 +43913,7 @@
           <t>C | 463呎 (2房)
 $1076万
 $23,229/呎
-(26年-08月-17日)</t>
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -43979,7 +43971,1508 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1280万
+$26,290/呎
+(26年-09月-04日)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1068万
+$23,076/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1085万
+$23,740/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$678万
+$27,116/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$887万
+$27,452/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$715万
+$28,490/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1264万
+$25,947/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1080万
+$23,637/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$674万
+$26,956/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$881万
+$27,288/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$711万
+$28,319/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1260万
+$25,871/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1078万
+$23,580/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$672万
+$26,872/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$879万
+$27,207/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$709万
+$28,235/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1256万
+$25,793/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1054万
+$22,760/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1069万
+$23,396/呎
+(25年-09月-12日)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$590万
+$23,580/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$876万
+$27,124/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$706万
+$28,147/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1262万
+$25,903/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1051万
+$22,691/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1066万
+$23,324/呎
+(24年-10月-29日)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$588万
+$23,508/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$769万
+$23,799/呎
+(26年-09月-06日)</t>
+        </is>
+      </c>
+      <c r="H11" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$704万
+$28,064/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1257万
+$25,807/呎
+(26年-08月-29日)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1047万
+$22,622/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1063万
+$23,254/呎
+(24年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$586万
+$23,440/呎
+(26年-02月-13日)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$766万
+$23,728/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$702万
+$27,980/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1254万
+$25,741/呎
+(26年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1044万
+$22,555/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1060万
+$23,186/呎
+(26年-04月-29日)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$584万
+$23,368/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$764万
+$23,659/呎
+(26年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$700万
+$27,896/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1242万
+$25,503/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1041万
+$22,488/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1056万
+$23,116/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$582万
+$23,296/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$762万
+$23,588/呎
+(26年-08月-28日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$698万
+$27,813/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1070万
+$23,305/呎
+(26年-07月-14日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1237万
+$25,409/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1038万
+$22,421/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1053万
+$23,046/呎
+(24年-10月-31日)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$581万
+$23,232/呎
+(24年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$760万
+$23,517/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$696万
+$27,729/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1066万
+$23,235/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1234万
+$25,333/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1035万
+$22,354/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1050万
+$22,978/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$579万
+$23,160/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$757万
+$23,446/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$694万
+$27,649/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1063万
+$23,166/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1226万
+$25,181/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1029万
+$22,222/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1044万
+$22,840/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$576万
+$23,024/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$753万
+$23,307/呎
+(26年-09月-02日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$690万
+$27,482/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J17" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1201万
+$26,166/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1236万
+$25,382/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1026万
+$22,156/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1041万
+$22,772/呎
+(24年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$574万
+$22,952/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$772万
+$23,895/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$605万
+$24,116/呎
+(26年-09月-07日)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1054万
+$22,959/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1233万
+$25,322/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1023万
+$22,089/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1038万
+$22,705/呎
+(24年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$588万
+$23,536/呎
+(22年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$748万
+$23,167/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$686万
+$27,319/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1080万
+$23,540/呎
+(22年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1230万
+$25,261/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1020万
+$22,022/呎
+(24年-07月-17日)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1064万
+$23,280/呎
+(22年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$587万
+$23,464/呎
+(22年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$746万
+$23,096/呎
+(26年-06月-15日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$684万
+$27,239/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1048万
+$22,821/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1227万
+$25,201/呎
+(26年-08月-25日)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1016万
+$21,955/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1172万
+$25,646/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$569万
+$22,748/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G21" s="25" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$845万
+$26,167/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I21" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$682万
+$27,155/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1044万
+$22,752/呎
+(26年-07月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1208万
+$24,807/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1014万
+$21,890/呎
+(24年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1058万
+$23,140/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$567万
+$22,680/呎
+(24年-12月-04日)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$742万
+$22,960/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$598万
+$23,829/呎
+(26年-08月-24日)</t>
+        </is>
+      </c>
+      <c r="J22" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1183万
+$25,778/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1204万
+$24,733/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1010万
+$21,825/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1025万
+$22,433/呎
+(24年-10月-31日)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$565万
+$22,612/呎
+(26年-03月-16日)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$739万
+$22,892/呎
+(26年-06月-10日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$678万
+$26,992/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J23" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1180万
+$25,699/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1201万
+$24,661/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1008万
+$21,760/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1022万
+$22,368/呎
+(24年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$564万
+$22,544/呎
+(26年-03月-24日)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$758万
+$23,471/呎
+(22年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$665万
+$26,510/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J24" s="23" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1158万
+$25,240/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1214万
+$24,934/呎
+(26年-08月-30日)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$1004万
+$21,685/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1016万
+$22,234/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$560万
+$22,412/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$733万
+$22,687/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$573万
+$22,845/呎
+(26年-08月-13日)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$998万
+$21,747/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -43987,7 +45480,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -43995,39 +45488,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$1068万
-$23,076/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
+$1000万
+$21,598/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1085万
-$23,740/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="F7" s="23" t="inlineStr">
+$1013万
+$22,166/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$678万
-$27,116/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G7" s="23" t="inlineStr">
+$559万
+$22,344/呎
+(26年-05月-11日)</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$887万
-$27,452/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
+$731万
+$22,619/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44035,1507 +45528,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$715万
-$28,490/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J7" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1264万
-$25,947/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1080万
-$23,637/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="F8" s="23" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$674万
-$26,956/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G8" s="23" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$881万
-$27,288/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$711万
-$28,319/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1260万
-$25,871/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1078万
-$23,580/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="F9" s="23" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$672万
-$26,872/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$879万
-$27,207/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I9" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$709万
-$28,235/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1256万
-$25,793/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1054万
-$22,760/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1069万
-$23,396/呎
-(25年-09月-12日)</t>
-        </is>
-      </c>
-      <c r="F10" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$590万
-$23,580/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$876万
-$27,124/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I10" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$706万
-$28,147/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1262万
-$25,903/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1051万
-$22,691/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1066万
-$23,324/呎
-(24年-10月-29日)</t>
-        </is>
-      </c>
-      <c r="F11" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$588万
-$23,508/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$874万
-$27,043/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I11" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$704万
-$28,064/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1257万
-$25,807/呎
-(26年-08月-29日)</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1047万
-$22,622/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1063万
-$23,254/呎
-(24年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="F12" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$586万
-$23,440/呎
-(26年-02月-13日)</t>
-        </is>
-      </c>
-      <c r="G12" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$766万
-$23,728/呎
-(26年-08月-22日)</t>
-        </is>
-      </c>
-      <c r="H12" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I12" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$702万
-$27,980/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1254万
-$25,741/呎
-(26年-08月-21日)</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1044万
-$22,555/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1060万
-$23,186/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="F13" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$584万
-$23,368/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G13" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$764万
-$23,659/呎
-(26年-08月-28日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I13" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$700万
-$27,896/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1242万
-$25,503/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1041万
-$22,488/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1056万
-$23,116/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$582万
-$23,296/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$762万
-$23,588/呎
-(26年-08月-28日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$698万
-$27,813/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J14" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1070万
-$23,305/呎
-(26年-07月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1237万
-$25,409/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1038万
-$22,421/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1053万
-$23,046/呎
-(24年-10月-31日)</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$581万
-$23,232/呎
-(24年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$760万
-$23,517/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$696万
-$27,729/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J15" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1066万
-$23,235/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1234万
-$25,333/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1035万
-$22,354/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1050万
-$22,978/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="F16" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$579万
-$23,160/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$757万
-$23,446/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="H16" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$694万
-$27,649/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J16" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1063万
-$23,166/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1226万
-$25,181/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1029万
-$22,222/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1044万
-$22,840/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="F17" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$576万
-$23,024/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G17" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$753万
-$23,307/呎
-(26年-09月-02日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$690万
-$27,482/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1201万
-$26,166/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1236万
-$25,382/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1026万
-$22,156/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1041万
-$22,772/呎
-(24年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F18" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$574万
-$22,952/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="G18" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$772万
-$23,895/呎
-(22年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$605万
-$24,116/呎
-(26年-08月-18日)</t>
-        </is>
-      </c>
-      <c r="J18" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1054万
-$22,959/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1233万
-$25,322/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1023万
-$22,089/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="E19" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1038万
-$22,705/呎
-(24年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="F19" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$588万
-$23,536/呎
-(22年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G19" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$748万
-$23,167/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$686万
-$27,319/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J19" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1080万
-$23,540/呎
-(22年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1230万
-$25,261/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1020万
-$22,022/呎
-(24年-07月-17日)</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1064万
-$23,280/呎
-(22年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="F20" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$587万
-$23,464/呎
-(22年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G20" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$746万
-$23,096/呎
-(26年-06月-15日)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$684万
-$27,239/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J20" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1048万
-$22,821/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1227万
-$25,201/呎
-(26年-08月-25日)</t>
-        </is>
-      </c>
-      <c r="C21" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1016万
-$21,955/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="E21" s="24" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1172万
-$25,646/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F21" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$569万
-$22,748/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G21" s="25" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$845万
-$26,167/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I21" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$682万
-$27,155/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J21" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1044万
-$22,752/呎
-(26年-07月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1208万
-$24,807/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1014万
-$21,890/呎
-(24年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1058万
-$23,140/呎
-(22年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F22" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$567万
-$22,680/呎
-(24年-12月-04日)</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$742万
-$22,960/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I22" s="20" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$598万
-$23,829/呎
-(26年-08月-24日)</t>
-        </is>
-      </c>
-      <c r="J22" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1183万
-$25,778/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1204万
-$24,733/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1010万
-$21,825/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1025万
-$22,433/呎
-(24年-10月-31日)</t>
-        </is>
-      </c>
-      <c r="F23" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$565万
-$22,612/呎
-(26年-03月-16日)</t>
-        </is>
-      </c>
-      <c r="G23" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$739万
-$22,892/呎
-(26年-06月-10日)</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I23" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$678万
-$26,992/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J23" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1180万
-$25,699/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1201万
-$24,661/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="C24" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1008万
-$21,760/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1022万
-$22,368/呎
-(24年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$564万
-$22,544/呎
-(26年-03月-24日)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$758万
-$23,471/呎
-(22年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="23" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$665万
-$26,510/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J24" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1158万
-$25,240/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-$1214万
-$24,934/呎
-(26年-08月-30日)</t>
-        </is>
-      </c>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1004万
-$21,685/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1016万
-$22,234/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$560万
-$22,412/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$733万
-$22,687/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="H25" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I25" s="20" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$573万
-$22,845/呎
-(26年-08月-13日)</t>
-        </is>
-      </c>
-      <c r="J25" s="20" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$998万
-$21,747/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$1000万
-$21,598/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$1013万
-$22,166/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$559万
-$22,344/呎
-(26年-05月-11日)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$731万
-$22,619/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
@@ -45544,12 +45536,12 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="J26" s="23" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1131万
-$24,638/呎
-(在售)</t>
+$995万
+$21,682/呎
+(26年-09月-05日)</t>
         </is>
       </c>
     </row>
@@ -46052,9 +46044,9 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 468呎 (2房)
+          <t>B | 467呎 (2房)
 $1191万
-$25,447/呎
+$25,501/呎
 (26年-08月-26日)</t>
         </is>
       </c>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -7020,7 +7020,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7029,14 +7029,14 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
         <v>10297000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>22984</v>
+        <v>22933</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>10297000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>22984</v>
+        <v>22933</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -24574,38 +24574,30 @@
       </c>
       <c r="F373" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H373" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I373" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H373" s="5" t="n">
+        <v>12114000</v>
+      </c>
+      <c r="I373" s="5" t="n">
+        <v>24875</v>
       </c>
       <c r="J373" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K373" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L373" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K373" s="5" t="n">
+        <v>12114000</v>
+      </c>
+      <c r="L373" s="5" t="n">
+        <v>24875</v>
       </c>
       <c r="M373" s="3" t="inlineStr">
         <is>
@@ -24614,7 +24606,7 @@
       </c>
       <c r="N373" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -43009,10 +43001,10 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 448呎 (2房)
+          <t>F | 449呎 (2房)
 $1030万
-$22,984/呎
-(26年-08月-19日)</t>
+$22,933/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -43731,7 +43723,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43741,7 +43733,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44292,7 +44284,7 @@
           <t>A | 487呎 (2房)
 $1262万
 $25,903/呎
-(26年-08月-22日)</t>
+(26年-09月-10日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -45472,12 +45464,12 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
+$1211万
+$24,875/呎
+(26年-09月-09日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -40091,7 +40091,7 @@
       </c>
       <c r="G621" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H621" s="5" t="n">
@@ -47930,7 +47930,7 @@
           <t>K | 329呎 (1房)
 $792万
 $24,079/呎
-(26年-08月-16日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -13027,7 +13027,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -18521,7 +18521,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -21833,7 +21833,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -34449,7 +34449,7 @@
       </c>
       <c r="G530" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="H530" s="5" t="n">
@@ -34883,7 +34883,7 @@
       </c>
       <c r="G537" s="3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="H537" s="5" t="n">
@@ -43889,7 +43889,7 @@
           <t>A | 487呎 (2房)
 $1284万
 $26,355/呎
-(26年-08月-24日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -44442,7 +44442,7 @@
           <t>A | 487呎 (2房)
 $1254万
 $25,741/呎
-(26年-08月-21日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -44719,7 +44719,7 @@
           <t>F | 323呎 (1房)
 $757万
 $23,446/呎
-(26年-08月-25日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -45209,7 +45209,7 @@
           <t>H | 251呎 (开放式)
 $598万
 $23,829/呎
-(26年-08月-24日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="J22" s="23" t="inlineStr">
@@ -46039,7 +46039,7 @@
           <t>B | 467呎 (2房)
 $1191万
 $25,501/呎
-(26年-08月-26日)</t>
+(26年-09月-15日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -46988,7 +46988,7 @@
           <t>A | 620呎 (3房)
 $1511万
 $24,374/呎
-(26年-08月-22日)</t>
+(26年-09月-17日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -47099,7 +47099,7 @@
           <t>D | 316呎 (1房)
 $734万
 $23,231/呎
-(26年-08月-23日)</t>
+(26年-09月-16日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -14458,34 +14458,34 @@
       </c>
       <c r="F215" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
-        <v>8788000</v>
+        <v>7734000</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>27207</v>
+        <v>23944</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K215" s="5" t="n">
-        <v>7733440</v>
+        <v>7734000</v>
       </c>
       <c r="L215" s="5" t="n">
-        <v>23943</v>
+        <v>23944</v>
       </c>
       <c r="M215" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N215" s="3" t="inlineStr">
@@ -16217,7 +16217,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -43723,7 +43723,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>37</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43733,7 +43733,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>118</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44161,12 +44161,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$879万
-$27,207/呎
-(在售)</t>
+$773万
+$23,944/呎
+(26年-09月-19日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -44363,7 +44363,7 @@
           <t>A | 487呎 (2房)
 $1257万
 $25,807/呎
-(26年-08月-29日)</t>
+(26年-09月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -44403,7 +44403,7 @@
           <t>F | 323呎 (1房)
 $766万
 $23,728/呎
-(26年-08月-22日)</t>
+(26年-09月-21日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -13348,34 +13348,34 @@
       </c>
       <c r="F198" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>6779000</v>
+        <v>5966000</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>27116</v>
+        <v>23864</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K198" s="5" t="n">
-        <v>5965520</v>
+        <v>5966000</v>
       </c>
       <c r="L198" s="5" t="n">
-        <v>23862</v>
+        <v>23864</v>
       </c>
       <c r="M198" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N198" s="3" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -24005,7 +24005,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -43723,7 +43723,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43733,7 +43733,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43995,12 +43995,12 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$678万
-$27,116/呎
-(在售)</t>
+$597万
+$23,864/呎
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="G7" s="23" t="inlineStr">
@@ -44324,7 +44324,7 @@
           <t>F | 323呎 (1房)
 $769万
 $23,799/呎
-(26年-09月-06日)</t>
+(26年-09月-24日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -45390,7 +45390,7 @@
           <t>A | 487呎 (2房)
 $1214万
 $24,934/呎
-(26年-08月-30日)</t>
+(26年-09月-22日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -123,13 +123,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="007F7F7F"/>
       <sz val="8"/>
     </font>
     <font>
@@ -285,10 +285,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -996,7 +996,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13609,7 +13609,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -25148,38 +25148,30 @@
       </c>
       <c r="F382" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H382" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I382" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="H382" s="5" t="n">
+        <v>12085000</v>
+      </c>
+      <c r="I382" s="5" t="n">
+        <v>24815</v>
       </c>
       <c r="J382" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K382" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L382" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K382" s="5" t="n">
+        <v>12085000</v>
+      </c>
+      <c r="L382" s="5" t="n">
+        <v>24815</v>
       </c>
       <c r="M382" s="3" t="inlineStr">
         <is>
@@ -25188,7 +25180,7 @@
       </c>
       <c r="N382" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26390,7 +26382,7 @@
       </c>
       <c r="F401" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G401" s="3" t="inlineStr">
@@ -26400,12 +26392,12 @@
       </c>
       <c r="H401" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I401" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J401" s="3" t="inlineStr">
@@ -26415,12 +26407,12 @@
       </c>
       <c r="K401" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L401" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M401" s="3" t="inlineStr">
@@ -26430,7 +26422,7 @@
       </c>
       <c r="N401" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26894,7 +26886,7 @@
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G409" s="3" t="inlineStr">
@@ -26904,12 +26896,12 @@
       </c>
       <c r="H409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J409" s="3" t="inlineStr">
@@ -26919,12 +26911,12 @@
       </c>
       <c r="K409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L409" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M409" s="3" t="inlineStr">
@@ -26934,7 +26926,7 @@
       </c>
       <c r="N409" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26956,7 @@
       </c>
       <c r="F410" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G410" s="3" t="inlineStr">
@@ -26974,12 +26966,12 @@
       </c>
       <c r="H410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J410" s="3" t="inlineStr">
@@ -26989,12 +26981,12 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M410" s="3" t="inlineStr">
@@ -27004,7 +26996,7 @@
       </c>
       <c r="N410" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -40029,7 +40021,7 @@
       </c>
       <c r="G620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H620" s="5" t="n">
@@ -42019,7 +42011,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -42039,7 +42031,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -42103,12 +42095,12 @@
       <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 484呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E5" s="22" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
         <is>
           <t>D | 318呎 (1房)
 -
@@ -42116,7 +42108,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="F5" s="22" t="inlineStr">
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42124,7 +42116,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 437呎 (2房)
 -
@@ -42172,7 +42164,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42180,7 +42172,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42235,7 +42227,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42243,7 +42235,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42298,7 +42290,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42306,7 +42298,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42361,7 +42353,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42369,7 +42361,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42424,7 +42416,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42432,7 +42424,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42487,7 +42479,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42495,7 +42487,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42550,7 +42542,7 @@
 (26年-06月-03日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42558,7 +42550,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42613,7 +42605,7 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42621,7 +42613,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -42676,7 +42668,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42739,7 +42731,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42802,7 +42794,7 @@
 (26年-05月-29日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42810,7 +42802,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -42865,7 +42857,7 @@
 (26年-05月-26日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42873,7 +42865,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -42928,7 +42920,7 @@
 (22年-10月-07日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -42936,7 +42928,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -42991,7 +42983,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43054,7 +43046,7 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43117,7 +43109,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43125,7 +43117,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -43180,7 +43172,7 @@
 (22年-10月-03日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43188,7 +43180,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -43243,7 +43235,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43251,7 +43243,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -43306,7 +43298,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43314,7 +43306,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -43369,7 +43361,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43377,7 +43369,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -43432,7 +43424,7 @@
 (22年-10月-05日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43440,7 +43432,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 招标单位
@@ -43495,7 +43487,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43503,7 +43495,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -43558,7 +43550,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43566,7 +43558,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -43621,7 +43613,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 433呎 (2房)
 -
@@ -43629,7 +43621,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 448呎 (2房)
 -
@@ -43723,7 +43715,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43733,7 +43725,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43805,7 +43797,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -43813,7 +43805,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -43821,7 +43813,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>C | 460呎 (2房)
 招标单位
@@ -43837,7 +43829,7 @@
 (26年-07月-17日)</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $682万
@@ -43845,7 +43837,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 -
@@ -43853,7 +43845,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -43869,7 +43861,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -43892,7 +43884,7 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -43916,7 +43908,7 @@
 (26年-07月-15日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $680万
@@ -43924,7 +43916,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $889万
@@ -43932,7 +43924,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -43948,7 +43940,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -43968,10 +43960,10 @@
           <t>A | 487呎 (2房)
 $1280万
 $26,290/呎
-(26年-09月-04日)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+(26年-09月-25日)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44003,7 +43995,7 @@
 (26年-09月-22日)</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $887万
@@ -44011,7 +44003,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H7" s="22" t="inlineStr">
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44027,7 +44019,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="J7" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44050,7 +44042,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44058,7 +44050,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
 招标单位
@@ -44074,7 +44066,7 @@
 (26年-07月-29日)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $674万
@@ -44082,7 +44074,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $881万
@@ -44090,7 +44082,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H8" s="22" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44106,7 +44098,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J8" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44129,7 +44121,7 @@
 (26年-07月-03日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44137,7 +44129,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
 招标单位
@@ -44153,7 +44145,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
 $672万
@@ -44169,7 +44161,7 @@
 (26年-09月-19日)</t>
         </is>
       </c>
-      <c r="H9" s="22" t="inlineStr">
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44185,7 +44177,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J9" s="23" t="inlineStr">
+      <c r="J9" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44208,7 +44200,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44240,7 +44232,7 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
 $876万
@@ -44248,7 +44240,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H10" s="22" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44264,7 +44256,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J10" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44287,7 +44279,7 @@
 (26年-09月-10日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44327,7 +44319,7 @@
 (26年-09月-24日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44343,7 +44335,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J11" s="23" t="inlineStr">
+      <c r="J11" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44366,7 +44358,7 @@
 (26年-09月-18日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44406,7 +44398,7 @@
 (26年-09月-21日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44422,7 +44414,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J12" s="23" t="inlineStr">
+      <c r="J12" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44445,7 +44437,7 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44485,7 +44477,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44501,7 +44493,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J13" s="23" t="inlineStr">
+      <c r="J13" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 招标单位
@@ -44524,7 +44516,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44564,7 +44556,7 @@
 (26年-08月-28日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44603,7 +44595,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44643,7 +44635,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44682,7 +44674,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44722,7 +44714,7 @@
 (26年-09月-15日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44761,7 +44753,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44801,7 +44793,7 @@
 (26年-09月-02日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44817,7 +44809,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J17" s="23" t="inlineStr">
+      <c r="J17" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 $1201万
@@ -44840,7 +44832,7 @@
 (26年-07月-24日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44880,7 +44872,7 @@
 (22年-10月-03日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44919,7 +44911,7 @@
 (26年-07月-28日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -44959,7 +44951,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -44967,7 +44959,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $686万
@@ -44998,7 +44990,7 @@
 (26年-07月-16日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45038,7 +45030,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45046,7 +45038,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I20" s="23" t="inlineStr">
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $684万
@@ -45077,7 +45069,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45117,7 +45109,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45125,7 +45117,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I21" s="23" t="inlineStr">
+      <c r="I21" s="22" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $682万
@@ -45156,7 +45148,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45196,7 +45188,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H22" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45212,7 +45204,7 @@
 (26年-09月-17日)</t>
         </is>
       </c>
-      <c r="J22" s="23" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 $1183万
@@ -45235,7 +45227,7 @@
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45275,7 +45267,7 @@
 (26年-06月-10日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45283,7 +45275,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $678万
@@ -45291,7 +45283,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J23" s="23" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 $1180万
@@ -45314,7 +45306,7 @@
 (26年-06月-16日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45354,7 +45346,7 @@
 (22年-10月-03日)</t>
         </is>
       </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H24" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45362,7 +45354,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
 $665万
@@ -45370,7 +45362,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="J24" s="23" t="inlineStr">
+      <c r="J24" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 $1158万
@@ -45393,7 +45385,7 @@
 (26年-09月-22日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45433,7 +45425,7 @@
 (26年-06月-09日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H25" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45472,7 +45464,7 @@
 (26年-09月-09日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45512,7 +45504,7 @@
 (26年-06月-11日)</t>
         </is>
       </c>
-      <c r="H26" s="22" t="inlineStr">
+      <c r="H26" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45543,7 +45535,86 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+$1208万
+$24,815/呎
+(26年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 433呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 463呎 (2房)
+$997万
+$21,542/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="inlineStr">
+        <is>
+          <t>D | 457呎 (2房)
+$1010万
+$22,101/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 250呎 (开放式)
+$556万
+$22,232/呎
+(24年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 323呎 (1房)
+$721万
+$22,325/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="H27" s="23" t="inlineStr">
+        <is>
+          <t>G | 436呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>H | 251呎 (开放式)
+$648万
+$25,801/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>J | 459呎 (2房)
+$1128万
+$24,564/呎
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -45551,7 +45622,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45559,39 +45630,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-$997万
-$21,542/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
+$981万
+$21,184/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 457呎 (2房)
-$1010万
-$22,101/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
+$995万
+$21,775/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 250呎 (开放式)
-$556万
-$22,232/呎
-(24年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
+$563万
+$22,524/呎
+(22年-10月-07日)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$721万
-$22,325/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
+$710万
+$21,997/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="H28" s="23" t="inlineStr">
         <is>
           <t>G | 436呎 (2房)
 -
@@ -45599,30 +45670,30 @@
 (待售)</t>
         </is>
       </c>
-      <c r="I27" s="24" t="inlineStr">
+      <c r="I28" s="24" t="inlineStr">
         <is>
           <t>H | 251呎 (开放式)
-$648万
-$25,801/呎
+$646万
+$25,725/呎
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J27" s="23" t="inlineStr">
+      <c r="J28" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
-$1128万
-$24,564/呎
+$1124万
+$24,490/呎
 (在售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 487呎 (2房)
 招标单位
@@ -45630,7 +45701,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 433呎 (2房)
 -
@@ -45638,85 +45709,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 463呎 (2房)
-$981万
-$21,184/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 457呎 (2房)
-$995万
-$21,775/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>E | 250呎 (开放式)
-$563万
-$22,524/呎
-(22年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 323呎 (1房)
-$710万
-$21,997/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>G | 436呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="24" t="inlineStr">
-        <is>
-          <t>H | 251呎 (开放式)
-$646万
-$25,725/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J28" s="23" t="inlineStr">
-        <is>
-          <t>J | 459呎 (2房)
-$1124万
-$24,490/呎
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B29" s="23" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>B | 433呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
@@ -45741,7 +45733,7 @@
 (26年-03月-16日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 285呎 (1房)
 -
@@ -45749,7 +45741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="H29" s="22" t="inlineStr">
+      <c r="H29" s="23" t="inlineStr">
         <is>
           <t>G | 398呎 (2房)
 -
@@ -45765,7 +45757,7 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="J29" s="23" t="inlineStr">
+      <c r="J29" s="22" t="inlineStr">
         <is>
           <t>J | 459呎 (2房)
 $1121万
@@ -45852,7 +45844,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45872,7 +45864,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -45942,17 +45934,17 @@
       <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C5" s="22" t="inlineStr">
+        <is>
+          <t>B | 468呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>B | 468呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -46014,9 +46006,9 @@
       <c r="K5" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
+招标单位
 -
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -46026,7 +46018,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -46098,7 +46090,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="K6" s="23" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $967万
@@ -46113,7 +46105,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -46185,7 +46177,7 @@
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $964万
@@ -46200,7 +46192,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -46272,7 +46264,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="K8" s="23" t="inlineStr">
+      <c r="K8" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $959万
@@ -46287,7 +46279,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -46311,7 +46303,7 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $860万
@@ -46359,7 +46351,7 @@
 (26年-06月-15日)</t>
         </is>
       </c>
-      <c r="K9" s="23" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $956万
@@ -46398,7 +46390,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $857万
@@ -46446,7 +46438,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $953万
@@ -46485,7 +46477,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $854万
@@ -46533,7 +46525,7 @@
 (24年-08月-02日)</t>
         </is>
       </c>
-      <c r="K11" s="23" t="inlineStr">
+      <c r="K11" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $950万
@@ -46572,7 +46564,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $852万
@@ -46620,7 +46612,7 @@
 (24年-11月-13日)</t>
         </is>
       </c>
-      <c r="K12" s="23" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $947万
@@ -46659,7 +46651,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $849万
@@ -47181,7 +47173,7 @@
 (26年-02月-25日)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $832万
@@ -47268,7 +47260,7 @@
 (26年-04月-20日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $829万
@@ -47355,7 +47347,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $827万
@@ -47616,7 +47608,7 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $819万
@@ -47703,7 +47695,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $814万
@@ -47771,7 +47763,7 @@
           <t>A | 620呎 (3房)
 $1467万
 $23,656/呎
-(26年-09月-02日)</t>
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -47790,7 +47782,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $812万
@@ -47853,7 +47845,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -47877,7 +47869,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="E27" s="23" t="inlineStr">
+      <c r="E27" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $810万
@@ -47940,7 +47932,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -47964,7 +47956,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E28" s="23" t="inlineStr">
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $802万
@@ -48012,7 +48004,7 @@
 (24年-06月-05日)</t>
         </is>
       </c>
-      <c r="K28" s="23" t="inlineStr">
+      <c r="K28" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $898万
@@ -48027,7 +48019,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -48051,7 +48043,7 @@
 (26年-06月-18日)</t>
         </is>
       </c>
-      <c r="E29" s="23" t="inlineStr">
+      <c r="E29" s="22" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
 $778万
@@ -48099,7 +48091,7 @@
 (24年-11月-05日)</t>
         </is>
       </c>
-      <c r="K29" s="23" t="inlineStr">
+      <c r="K29" s="22" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
 $895万

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -24067,7 +24067,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -40636,38 +40636,30 @@
       </c>
       <c r="F630" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H630" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I630" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="H630" s="5" t="n">
+        <v>14623000</v>
+      </c>
+      <c r="I630" s="5" t="n">
+        <v>23585</v>
       </c>
       <c r="J630" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K630" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L630" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K630" s="5" t="n">
+        <v>14623000</v>
+      </c>
+      <c r="L630" s="5" t="n">
+        <v>23585</v>
       </c>
       <c r="M630" s="3" t="inlineStr">
         <is>
@@ -40676,7 +40668,7 @@
       </c>
       <c r="N630" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -40706,23 +40698,23 @@
       </c>
       <c r="F631" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
-        <v>8975000</v>
+        <v>7898000</v>
       </c>
       <c r="I631" s="5" t="n">
-        <v>27280</v>
+        <v>24006</v>
       </c>
       <c r="J631" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K631" s="5" t="n">
@@ -40733,7 +40725,7 @@
       </c>
       <c r="M631" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N631" s="3" t="inlineStr">
@@ -45461,7 +45453,7 @@
           <t>A | 487呎 (2房)
 $1211万
 $24,875/呎
-(26年-09月-09日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -45525,7 +45517,7 @@
           <t>J | 459呎 (2房)
 $995万
 $21,682/呎
-(26年-09月-05日)</t>
+(26年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -45844,7 +45836,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45854,7 +45846,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>210</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -47845,7 +47837,94 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 620呎 (3房)
+$1462万
+$23,585/呎
+(26年-09月-28日)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 467呎 (2房)
+$1104万
+$23,649/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 443呎 (2房)
+$1031万
+$23,269/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 317呎 (1房)
+$810万
+$25,536/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F27" s="20" t="inlineStr">
+        <is>
+          <t>E | 325呎 (1房)
+$715万
+$21,994/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>F | 461呎 (2房)
+$1012万
+$21,944/呎
+(26年-06月-16日)</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>G | 450呎 (2房)
+$1002万
+$22,276/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="I27" s="20" t="inlineStr">
+        <is>
+          <t>H | 315呎 (1房)
+$701万
+$22,267/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="J27" s="20" t="inlineStr">
+        <is>
+          <t>J | 316呎 (1房)
+$753万
+$23,842/呎
+(24年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>K | 329呎 (1房)
+$792万
+$24,079/呎
+(26年-09月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
 招标单位
@@ -47853,93 +47932,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>B | 467呎 (2房)
-$1104万
-$23,649/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>C | 443呎 (2房)
-$1031万
-$23,269/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>D | 317呎 (1房)
-$810万
-$25,536/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 325呎 (1房)
-$715万
-$21,994/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 461呎 (2房)
-$1012万
-$21,944/呎
-(26年-06月-16日)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 450呎 (2房)
-$1002万
-$22,276/呎
-(26年-05月-29日)</t>
-        </is>
-      </c>
-      <c r="I27" s="20" t="inlineStr">
-        <is>
-          <t>H | 315呎 (1房)
-$701万
-$22,267/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="J27" s="20" t="inlineStr">
-        <is>
-          <t>J | 316呎 (1房)
-$753万
-$23,842/呎
-(24年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>K | 329呎 (1房)
-$792万
-$24,079/呎
-(26年-09月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B28" s="22" t="inlineStr">
-        <is>
-          <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 467呎 (2房)
@@ -48004,12 +47996,12 @@
 (24年-06月-05日)</t>
         </is>
       </c>
-      <c r="K28" s="22" t="inlineStr">
+      <c r="K28" s="20" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
-$898万
-$27,280/呎
-(在售)</t>
+$790万
+$24,006/呎
+(26年-10月-04日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -29282,34 +29282,34 @@
       </c>
       <c r="F447" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
-        <v>8595000</v>
+        <v>7564000</v>
       </c>
       <c r="I447" s="5" t="n">
-        <v>27114</v>
+        <v>23861</v>
       </c>
       <c r="J447" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K447" s="5" t="n">
-        <v>7563600</v>
+        <v>7564000</v>
       </c>
       <c r="L447" s="5" t="n">
-        <v>23860</v>
+        <v>23861</v>
       </c>
       <c r="M447" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N447" s="3" t="inlineStr">
@@ -41256,38 +41256,30 @@
       </c>
       <c r="F640" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G640" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H640" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I640" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H640" s="5" t="n">
+        <v>14579000</v>
+      </c>
+      <c r="I640" s="5" t="n">
+        <v>23515</v>
       </c>
       <c r="J640" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K640" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L640" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K640" s="5" t="n">
+        <v>14579000</v>
+      </c>
+      <c r="L640" s="5" t="n">
+        <v>23515</v>
       </c>
       <c r="M640" s="3" t="inlineStr">
         <is>
@@ -41296,7 +41288,7 @@
       </c>
       <c r="N640" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -45836,7 +45828,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45846,7 +45838,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>212</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46295,12 +46287,12 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
-$860万
-$27,114/呎
-(在售)</t>
+$756万
+$23,861/呎
+(26年-10月-06日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -47924,12 +47916,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 620呎 (3房)
-招标单位
--
-(在售)</t>
+$1458万
+$23,515/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -14644,38 +14644,30 @@
       </c>
       <c r="F218" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H218" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I218" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="H218" s="5" t="n">
+        <v>10631000</v>
+      </c>
+      <c r="I218" s="5" t="n">
+        <v>22961</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K218" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L218" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K218" s="5" t="n">
+        <v>10631000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>22961</v>
       </c>
       <c r="M218" s="3" t="inlineStr">
         <is>
@@ -14684,7 +14676,7 @@
       </c>
       <c r="N218" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30778,34 +30770,34 @@
       </c>
       <c r="F471" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
-        <v>9472000</v>
+        <v>8336000</v>
       </c>
       <c r="I471" s="5" t="n">
-        <v>28790</v>
+        <v>25337</v>
       </c>
       <c r="J471" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K471" s="5" t="n">
-        <v>8335360</v>
+        <v>8336000</v>
       </c>
       <c r="L471" s="5" t="n">
-        <v>25335</v>
+        <v>25337</v>
       </c>
       <c r="M471" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N471" s="3" t="inlineStr">
@@ -40450,34 +40442,34 @@
       </c>
       <c r="F627" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G627" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="H627" s="5" t="n">
-        <v>8095000</v>
+        <v>7124000</v>
       </c>
       <c r="I627" s="5" t="n">
-        <v>25536</v>
+        <v>22473</v>
       </c>
       <c r="J627" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K627" s="5" t="n">
-        <v>7123600</v>
+        <v>7124000</v>
       </c>
       <c r="L627" s="5" t="n">
-        <v>22472</v>
+        <v>22473</v>
       </c>
       <c r="M627" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N627" s="3" t="inlineStr">
@@ -43699,7 +43691,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43709,7 +43701,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -44113,12 +44105,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 463呎 (2房)
-招标单位
--
-(在售)</t>
+$1063万
+$22,961/呎
+(26年-10月-11日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -45828,7 +45820,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45838,7 +45830,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>214</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -46596,12 +46588,12 @@
 (24年-11月-13日)</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="20" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
-$947万
-$28,790/呎
-(在售)</t>
+$834万
+$25,337/呎
+(26年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -47853,12 +47845,12 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 317呎 (1房)
-$810万
-$25,536/呎
-(在售)</t>
+$712万
+$22,473/呎
+(26年-10月-10日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -14463,7 +14463,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -44134,7 +44134,7 @@
           <t>F | 323呎 (1房)
 $773万
 $23,944/呎
-(26年-09月-19日)</t>
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -5670,42 +5670,34 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>10421000</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>23209</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L79" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K79" s="5" t="n">
+        <v>10421000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>23209</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5714,7 +5706,7 @@
       </c>
       <c r="N79" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13353,7 +13345,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -15040,34 +15032,34 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
-        <v>8761000</v>
+        <v>7710000</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>27124</v>
+        <v>23870</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K224" s="5" t="n">
-        <v>7709680</v>
+        <v>7710000</v>
       </c>
       <c r="L224" s="5" t="n">
-        <v>23869</v>
+        <v>23870</v>
       </c>
       <c r="M224" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N224" s="3" t="inlineStr">
@@ -25145,7 +25137,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -40633,7 +40625,7 @@
       </c>
       <c r="G630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H630" s="5" t="n">
@@ -40695,7 +40687,7 @@
       </c>
       <c r="G631" s="3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H631" s="5" t="n">
@@ -41253,7 +41245,7 @@
       </c>
       <c r="G640" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="H640" s="5" t="n">
@@ -41987,7 +41979,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41997,7 +41989,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42778,12 +42770,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
-        <is>
-          <t>F | 448呎 (2房)
-招标单位
--
-(在售)</t>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>F | 449呎 (2房)
+$1042万
+$23,209/呎
+(26年-10月-18日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -43691,7 +43683,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -43701,7 +43693,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -43968,7 +43960,7 @@
           <t>E | 250呎 (开放式)
 $597万
 $23,864/呎
-(26年-09月-22日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -44208,12 +44200,12 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 323呎 (1房)
-$876万
-$27,124/呎
-(在售)</t>
+$771万
+$23,870/呎
+(26年-10月-19日)</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -45516,7 +45508,7 @@
           <t>A | 487呎 (2房)
 $1208万
 $24,815/呎
-(26年-09月-26日)</t>
+(26年-10月-21日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -47826,7 +47818,7 @@
           <t>A | 620呎 (3房)
 $1462万
 $23,585/呎
-(26年-09月-28日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -47913,7 +47905,7 @@
           <t>A | 620呎 (3房)
 $1458万
 $23,515/呎
-(26年-10月-05日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -47985,7 +47977,7 @@
           <t>K | 329呎 (1房)
 $790万
 $24,006/呎
-(26年-10月-04日)</t>
+(26年-10月-26日)</t>
         </is>
       </c>
     </row>

--- a/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
+++ b/九龙-启德-Miami Quay I/Miami Quay I_销控明细表.xlsx
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>12830000</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>25711</v>
+        <v>25660</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>12830000</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>25711</v>
+        <v>25660</v>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         <v>12843000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>26480</v>
+        <v>26426</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>12843000</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26480</v>
+        <v>26426</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>12798000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>25647</v>
+        <v>25596</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>12798000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>25647</v>
+        <v>25596</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1854,7 +1854,7 @@
         <v>12805000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>26402</v>
+        <v>26348</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>12805000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>26402</v>
+        <v>26348</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>12683000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>25417</v>
+        <v>25366</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>12683000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>25417</v>
+        <v>25366</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
         <v>12729000</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>26245</v>
+        <v>26191</v>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>12729000</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>26245</v>
+        <v>26191</v>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>12645000</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>25341</v>
+        <v>25290</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>12645000</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>25341</v>
+        <v>25290</v>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
         <v>12691000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>26167</v>
+        <v>26113</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>12691000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>26167</v>
+        <v>26113</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>12607000</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>25265</v>
+        <v>25214</v>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>12607000</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>25265</v>
+        <v>25214</v>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>12652000</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>26087</v>
+        <v>26033</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
         <v>12652000</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>26087</v>
+        <v>26033</v>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>12638000</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>25327</v>
+        <v>25276</v>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>12638000</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>25327</v>
+        <v>25276</v>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         <v>12614000</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>26008</v>
+        <v>25955</v>
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>12614000</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>26008</v>
+        <v>25955</v>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
@@ -3824,7 +3824,7 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>12605000</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>25261</v>
+        <v>25210</v>
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>12605000</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>25261</v>
+        <v>25210</v>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
@@ -4088,7 +4088,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>12577000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>25932</v>
+        <v>25879</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>12577000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>25932</v>
+        <v>25879</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>12573000</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>25196</v>
+        <v>25146</v>
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>12573000</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>25196</v>
+        <v>25146</v>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>12540000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>25856</v>
+        <v>25802</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4565,7 +4565,7 @@
         <v>12540000</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>25856</v>
+        <v>25802</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>12458000</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>24966</v>
+        <v>24916</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4751,7 +4751,7 @@
         <v>12458000</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>24966</v>
+        <v>24916</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4786,7 +4786,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>10483000</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>23347</v>
+        <v>23400</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>10483000</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>23347</v>
+        <v>23400</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
         <v>12502000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>25777</v>
+        <v>25724</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>12502000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>25777</v>
+        <v>25724</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>12420000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>24890</v>
+        <v>24840</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>12420000</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>24890</v>
+        <v>24840</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -5244,7 +5244,7 @@
         <v>10452000</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>23278</v>
+        <v>23330</v>
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>10452000</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>23278</v>
+        <v>23330</v>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
@@ -5422,7 +5422,7 @@
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>12465000</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>25701</v>
+        <v>25648</v>
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>12465000</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>25701</v>
+        <v>25648</v>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
@@ -5608,7 +5608,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>12383000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>24816</v>
+        <v>24766</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>12383000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>24816</v>
+        <v>24766</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>10421000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>23209</v>
+        <v>23261</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>10421000</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>23209</v>
+        <v>23261</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -6066,7 +6066,7 @@
         <v>12309000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>24667</v>
+        <v>24618</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -6077,7 +6077,7 @@
         <v>12309000</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>24667</v>
+        <v>24618</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>12353000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>25470</v>
+        <v>25418</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>12353000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>25470</v>
+        <v>25418</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="E92" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>12272000</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>24593</v>
+        <v>24544</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>12272000</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>24593</v>
+        <v>24544</v>
       </c>
       <c r="M92" s="3" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="E96" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>12316000</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>25394</v>
+        <v>25342</v>
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>12316000</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>25394</v>
+        <v>25342</v>
       </c>
       <c r="M96" s="3" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="E99" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>12236000</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>24521</v>
+        <v>24472</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         <v>12236000</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>24521</v>
+        <v>24472</v>
       </c>
       <c r="M99" s="3" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>10297000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>22933</v>
+        <v>22984</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>10297000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>22933</v>
+        <v>22984</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>12279000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>25318</v>
+        <v>25265</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>12279000</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>25318</v>
+        <v>25265</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         </is>
       </c>
       <c r="E106" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
@@ -7408,7 +7408,7 @@
         <v>12339000</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>24727</v>
+        <v>24678</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>12339000</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>24727</v>
+        <v>24678</v>
       </c>
       <c r="M106" s="3" t="inlineStr">
         <is>
@@ -7454,7 +7454,7 @@
         </is>
       </c>
       <c r="E107" s="4" t="n">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>10266000</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>22864</v>
+        <v>22915</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>10266000</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>22864</v>
+        <v>22915</v>
       </c>
       <c r="M107" s="3" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         </is>
       </c>
       <c r="E110" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F110" s="3" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>12243000</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>25243</v>
+        <v>25191</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
         <v>12243000</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>25243</v>
+        <v>25191</v>
       </c>
       <c r="M110" s="3" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         </is>
       </c>
       <c r="E113" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>12309000</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>24667</v>
+        <v>24618</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>12309000</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>24667</v>
+        <v>24618</v>
       </c>
       <c r="M113" s="3" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="E117" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>12206000</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>25167</v>
+        <v>25115</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>12206000</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>25167</v>
+        <v>25115</v>
       </c>
       <c r="M117" s="3" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="E120" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F120" s="3" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         <v>12126000</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>24301</v>
+        <v>24252</v>
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         <v>12126000</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>24301</v>
+        <v>24252</v>
       </c>
       <c r="M120" s="3" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>12090000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>24228</v>
+        <v>24180</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>12090000</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>24228</v>
+        <v>24180</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -9014,7 +9014,7 @@
         <v>12133000</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>25016</v>
+        <v>24965</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>12133000</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>25016</v>
+        <v>24965</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         <v>12054000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>24156</v>
+        <v>24108</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>12054000</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>24156</v>
+        <v>24108</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         </is>
       </c>
       <c r="E138" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>12097000</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>24942</v>
+        <v>24891</v>
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>12097000</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>24942</v>
+        <v>24891</v>
       </c>
       <c r="M138" s="3" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9650,7 +9650,7 @@
         <v>12179000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>24407</v>
+        <v>24358</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9661,7 +9661,7 @@
         <v>12179000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>24407</v>
+        <v>24358</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>12025000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>24794</v>
+        <v>24743</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9925,7 +9925,7 @@
         <v>12025000</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>24794</v>
+        <v>24743</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         </is>
       </c>
       <c r="E148" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>12150000</v>
       </c>
       <c r="I148" s="5" t="n">
-        <v>24349</v>
+        <v>24300</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>12150000</v>
       </c>
       <c r="L148" s="5" t="n">
-        <v>24349</v>
+        <v>24300</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         </is>
       </c>
       <c r="E152" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>11989000</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>24720</v>
+        <v>24669</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -10375,7 +10375,7 @@
         <v>11989000</v>
       </c>
       <c r="L152" s="5" t="n">
-        <v>24720</v>
+        <v>24669</v>
       </c>
       <c r="M152" s="3" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>12121000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>24291</v>
+        <v>24242</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -10561,7 +10561,7 @@
         <v>12121000</v>
       </c>
       <c r="L155" s="5" t="n">
-        <v>24291</v>
+        <v>24242</v>
       </c>
       <c r="M155" s="3" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>11953000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>24645</v>
+        <v>24595</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10825,7 +10825,7 @@
         <v>11953000</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>24645</v>
+        <v>24595</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         </is>
       </c>
       <c r="E162" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>12091000</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>24230</v>
+        <v>24182</v>
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>12091000</v>
       </c>
       <c r="L162" s="5" t="n">
-        <v>24230</v>
+        <v>24182</v>
       </c>
       <c r="M162" s="3" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="E166" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>11917000</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>24571</v>
+        <v>24521</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>11917000</v>
       </c>
       <c r="L166" s="5" t="n">
-        <v>24571</v>
+        <v>24521</v>
       </c>
       <c r="M166" s="3" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         </is>
       </c>
       <c r="E169" s="4" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         <v>12062000</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>24172</v>
+        <v>24124</v>
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>12062000</v>
       </c>
       <c r="L169" s="5" t="n">
-        <v>24172</v>
+        <v>24124</v>
       </c>
       <c r="M169" s="3" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         </is>
       </c>
       <c r="E173" s="4" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F173" s="3" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>11881000</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>24497</v>
+        <v>24447</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>11881000</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>24497</v>
+        <v>24447</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         </is>
       </c>
       <c r="E402" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F402" s="3" t="inlineStr">
         <is>
@@ -26448,7 +26448,7 @@
         <v>8119000</v>
       </c>
       <c r="I402" s="5" t="n">
-        <v>25693</v>
+        <v>25612</v>
       </c>
       <c r="J402" s="3" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>8119000</v>
       </c>
       <c r="L402" s="5" t="n">
-        <v>25693</v>
+        <v>25612</v>
       </c>
       <c r="M402" s="3" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         </is>
       </c>
       <c r="E405" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F405" s="3" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>10900000</v>
       </c>
       <c r="I405" s="5" t="n">
-        <v>23644</v>
+        <v>23696</v>
       </c>
       <c r="J405" s="3" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>10900000</v>
       </c>
       <c r="L405" s="5" t="n">
-        <v>23644</v>
+        <v>23696</v>
       </c>
       <c r="M405" s="3" t="inlineStr">
         <is>
@@ -27010,34 +27010,34 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
-        <v>9673000</v>
+        <v>8513000</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>29401</v>
+        <v>25875</v>
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K411" s="5" t="n">
-        <v>8512240</v>
+        <v>8513000</v>
       </c>
       <c r="L411" s="5" t="n">
-        <v>25873</v>
+        <v>25875</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N411" s="3" t="inlineStr">
@@ -27068,7 +27068,7 @@
         </is>
       </c>
       <c r="E412" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F412" s="3" t="inlineStr">
         <is>
@@ -27084,7 +27084,7 @@
         <v>8096000</v>
       </c>
       <c r="I412" s="5" t="n">
-        <v>25620</v>
+        <v>25539</v>
       </c>
       <c r="J412" s="3" t="inlineStr">
         <is>
@@ -27095,7 +27095,7 @@
         <v>8096000</v>
       </c>
       <c r="L412" s="5" t="n">
-        <v>25620</v>
+        <v>25539</v>
       </c>
       <c r="M412" s="3" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         </is>
       </c>
       <c r="E415" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F415" s="3" t="inlineStr">
         <is>
@@ -27270,7 +27270,7 @@
         <v>10874000</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>23588</v>
+        <v>23639</v>
       </c>
       <c r="J415" s="3" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>10874000</v>
       </c>
       <c r="L415" s="5" t="n">
-        <v>23588</v>
+        <v>23639</v>
       </c>
       <c r="M415" s="3" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         </is>
       </c>
       <c r="E419" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F419" s="3" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>11909000</v>
       </c>
       <c r="I419" s="5" t="n">
-        <v>25501</v>
+        <v>25447</v>
       </c>
       <c r="J419" s="3" t="inlineStr">
         <is>
@@ -27529,7 +27529,7 @@
         <v>11909000</v>
       </c>
       <c r="L419" s="5" t="n">
-        <v>25501</v>
+        <v>25447</v>
       </c>
       <c r="M419" s="3" t="inlineStr">
         <is>
@@ -27696,7 +27696,7 @@
         </is>
       </c>
       <c r="E422" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>8071000</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>25541</v>
+        <v>25461</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>8071000</v>
       </c>
       <c r="L422" s="5" t="n">
-        <v>25541</v>
+        <v>25461</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         </is>
       </c>
       <c r="E425" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F425" s="3" t="inlineStr">
         <is>
@@ -27898,7 +27898,7 @@
         <v>10854000</v>
       </c>
       <c r="I425" s="5" t="n">
-        <v>23544</v>
+        <v>23596</v>
       </c>
       <c r="J425" s="3" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>10854000</v>
       </c>
       <c r="L425" s="5" t="n">
-        <v>23544</v>
+        <v>23596</v>
       </c>
       <c r="M425" s="3" t="inlineStr">
         <is>
@@ -28130,7 +28130,7 @@
         </is>
       </c>
       <c r="E429" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F429" s="3" t="inlineStr">
         <is>
@@ -28146,7 +28146,7 @@
         <v>11832000</v>
       </c>
       <c r="I429" s="5" t="n">
-        <v>25336</v>
+        <v>25282</v>
       </c>
       <c r="J429" s="3" t="inlineStr">
         <is>
@@ -28157,7 +28157,7 @@
         <v>11832000</v>
       </c>
       <c r="L429" s="5" t="n">
-        <v>25336</v>
+        <v>25282</v>
       </c>
       <c r="M429" s="3" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="E432" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F432" s="3" t="inlineStr">
         <is>
@@ -28340,7 +28340,7 @@
         <v>8023000</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>25389</v>
+        <v>25309</v>
       </c>
       <c r="J432" s="3" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>8023000</v>
       </c>
       <c r="L432" s="5" t="n">
-        <v>25389</v>
+        <v>25309</v>
       </c>
       <c r="M432" s="3" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         </is>
       </c>
       <c r="E435" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F435" s="3" t="inlineStr">
         <is>
@@ -28526,7 +28526,7 @@
         <v>10807000</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>23443</v>
+        <v>23493</v>
       </c>
       <c r="J435" s="3" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>10807000</v>
       </c>
       <c r="L435" s="5" t="n">
-        <v>23443</v>
+        <v>23493</v>
       </c>
       <c r="M435" s="3" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         </is>
       </c>
       <c r="E439" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F439" s="3" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>11762000</v>
       </c>
       <c r="I439" s="5" t="n">
-        <v>25186</v>
+        <v>25132</v>
       </c>
       <c r="J439" s="3" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>11762000</v>
       </c>
       <c r="L439" s="5" t="n">
-        <v>25186</v>
+        <v>25132</v>
       </c>
       <c r="M439" s="3" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         </is>
       </c>
       <c r="E442" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F442" s="3" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>7999000</v>
       </c>
       <c r="I442" s="5" t="n">
-        <v>25313</v>
+        <v>25233</v>
       </c>
       <c r="J442" s="3" t="inlineStr">
         <is>
@@ -28979,7 +28979,7 @@
         <v>7999000</v>
       </c>
       <c r="L442" s="5" t="n">
-        <v>25313</v>
+        <v>25233</v>
       </c>
       <c r="M442" s="3" t="inlineStr">
         <is>
@@ -29138,7 +29138,7 @@
         </is>
       </c>
       <c r="E445" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F445" s="3" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>10781000</v>
       </c>
       <c r="I445" s="5" t="n">
-        <v>23386</v>
+        <v>23437</v>
       </c>
       <c r="J445" s="3" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>10781000</v>
       </c>
       <c r="L445" s="5" t="n">
-        <v>23386</v>
+        <v>23437</v>
       </c>
       <c r="M445" s="3" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         </is>
       </c>
       <c r="E449" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F449" s="3" t="inlineStr">
         <is>
@@ -29402,7 +29402,7 @@
         <v>11726000</v>
       </c>
       <c r="I449" s="5" t="n">
-        <v>25109</v>
+        <v>25056</v>
       </c>
       <c r="J449" s="3" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>11726000</v>
       </c>
       <c r="L449" s="5" t="n">
-        <v>25109</v>
+        <v>25056</v>
       </c>
       <c r="M449" s="3" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         </is>
       </c>
       <c r="E452" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F452" s="3" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>7975000</v>
       </c>
       <c r="I452" s="5" t="n">
-        <v>25237</v>
+        <v>25158</v>
       </c>
       <c r="J452" s="3" t="inlineStr">
         <is>
@@ -29607,7 +29607,7 @@
         <v>7975000</v>
       </c>
       <c r="L452" s="5" t="n">
-        <v>25237</v>
+        <v>25158</v>
       </c>
       <c r="M452" s="3" t="inlineStr">
         <is>
@@ -29766,7 +29766,7 @@
         </is>
       </c>
       <c r="E455" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F455" s="3" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>10755000</v>
       </c>
       <c r="I455" s="5" t="n">
-        <v>23330</v>
+        <v>23380</v>
       </c>
       <c r="J455" s="3" t="inlineStr">
         <is>
@@ -29793,7 +29793,7 @@
         <v>10755000</v>
       </c>
       <c r="L455" s="5" t="n">
-        <v>23330</v>
+        <v>23380</v>
       </c>
       <c r="M455" s="3" t="inlineStr">
         <is>
@@ -30014,7 +30014,7 @@
         </is>
       </c>
       <c r="E459" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F459" s="3" t="inlineStr">
         <is>
@@ -30030,7 +30030,7 @@
         <v>11691000</v>
       </c>
       <c r="I459" s="5" t="n">
-        <v>25034</v>
+        <v>24981</v>
       </c>
       <c r="J459" s="3" t="inlineStr">
         <is>
@@ -30041,7 +30041,7 @@
         <v>11691000</v>
       </c>
       <c r="L459" s="5" t="n">
-        <v>25034</v>
+        <v>24981</v>
       </c>
       <c r="M459" s="3" t="inlineStr">
         <is>
@@ -30200,7 +30200,7 @@
         </is>
       </c>
       <c r="E462" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
@@ -30216,7 +30216,7 @@
         <v>7951000</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>25161</v>
+        <v>25082</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>7951000</v>
       </c>
       <c r="L462" s="5" t="n">
-        <v>25161</v>
+        <v>25082</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
@@ -30386,7 +30386,7 @@
         </is>
       </c>
       <c r="E465" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F465" s="3" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>10729000</v>
       </c>
       <c r="I465" s="5" t="n">
-        <v>23273</v>
+        <v>23324</v>
       </c>
       <c r="J465" s="3" t="inlineStr">
         <is>
@@ -30413,7 +30413,7 @@
         <v>10729000</v>
       </c>
       <c r="L465" s="5" t="n">
-        <v>23273</v>
+        <v>23324</v>
       </c>
       <c r="M465" s="3" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         </is>
       </c>
       <c r="E469" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F469" s="3" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>11656000</v>
       </c>
       <c r="I469" s="5" t="n">
-        <v>24959</v>
+        <v>24906</v>
       </c>
       <c r="J469" s="3" t="inlineStr">
         <is>
@@ -30661,7 +30661,7 @@
         <v>11656000</v>
       </c>
       <c r="L469" s="5" t="n">
-        <v>24959</v>
+        <v>24906</v>
       </c>
       <c r="M469" s="3" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         </is>
       </c>
       <c r="E472" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F472" s="3" t="inlineStr">
         <is>
@@ -30836,7 +30836,7 @@
         <v>7928000</v>
       </c>
       <c r="I472" s="5" t="n">
-        <v>25089</v>
+        <v>25009</v>
       </c>
       <c r="J472" s="3" t="inlineStr">
         <is>
@@ -30847,7 +30847,7 @@
         <v>7928000</v>
       </c>
       <c r="L472" s="5" t="n">
-        <v>25089</v>
+        <v>25009</v>
       </c>
       <c r="M472" s="3" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         </is>
       </c>
       <c r="E475" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F475" s="3" t="inlineStr">
         <is>
@@ -31022,7 +31022,7 @@
         <v>10704000</v>
       </c>
       <c r="I475" s="5" t="n">
-        <v>23219</v>
+        <v>23270</v>
       </c>
       <c r="J475" s="3" t="inlineStr">
         <is>
@@ -31033,7 +31033,7 @@
         <v>10704000</v>
       </c>
       <c r="L475" s="5" t="n">
-        <v>23219</v>
+        <v>23270</v>
       </c>
       <c r="M475" s="3" t="inlineStr">
         <is>
@@ -31254,7 +31254,7 @@
         </is>
       </c>
       <c r="E479" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F479" s="3" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>11952000</v>
       </c>
       <c r="I479" s="5" t="n">
-        <v>25593</v>
+        <v>25538</v>
       </c>
       <c r="J479" s="3" t="inlineStr">
         <is>
@@ -31281,7 +31281,7 @@
         <v>11952000</v>
       </c>
       <c r="L479" s="5" t="n">
-        <v>25593</v>
+        <v>25538</v>
       </c>
       <c r="M479" s="3" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         </is>
       </c>
       <c r="E485" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F485" s="3" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>10678000</v>
       </c>
       <c r="I485" s="5" t="n">
-        <v>23163</v>
+        <v>23213</v>
       </c>
       <c r="J485" s="3" t="inlineStr">
         <is>
@@ -31653,7 +31653,7 @@
         <v>10678000</v>
       </c>
       <c r="L485" s="5" t="n">
-        <v>23163</v>
+        <v>23213</v>
       </c>
       <c r="M485" s="3" t="inlineStr">
         <is>
@@ -32246,7 +32246,7 @@
         </is>
       </c>
       <c r="E495" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F495" s="3" t="inlineStr">
         <is>
@@ -32262,7 +32262,7 @@
         <v>10652000</v>
       </c>
       <c r="I495" s="5" t="n">
-        <v>23106</v>
+        <v>23157</v>
       </c>
       <c r="J495" s="3" t="inlineStr">
         <is>
@@ -32273,7 +32273,7 @@
         <v>10652000</v>
       </c>
       <c r="L495" s="5" t="n">
-        <v>23106</v>
+        <v>23157</v>
       </c>
       <c r="M495" s="3" t="inlineStr">
         <is>
@@ -32866,7 +32866,7 @@
         </is>
       </c>
       <c r="E505" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F505" s="3" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>10627000</v>
       </c>
       <c r="I505" s="5" t="n">
-        <v>23052</v>
+        <v>23102</v>
       </c>
       <c r="J505" s="3" t="inlineStr">
         <is>
@@ -32893,7 +32893,7 @@
         <v>10627000</v>
       </c>
       <c r="L505" s="5" t="n">
-        <v>23052</v>
+        <v>23102</v>
       </c>
       <c r="M505" s="3" t="inlineStr">
         <is>
@@ -33114,7 +33114,7 @@
         </is>
       </c>
       <c r="E509" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F509" s="3" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>11518000</v>
       </c>
       <c r="I509" s="5" t="n">
-        <v>24664</v>
+        <v>24611</v>
       </c>
       <c r="J509" s="3" t="inlineStr">
         <is>
@@ -33141,7 +33141,7 @@
         <v>11518000</v>
       </c>
       <c r="L509" s="5" t="n">
-        <v>24664</v>
+        <v>24611</v>
       </c>
       <c r="M509" s="3" t="inlineStr">
         <is>
@@ -33486,7 +33486,7 @@
         </is>
       </c>
       <c r="E515" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
@@ -33502,7 +33502,7 @@
         <v>10612000</v>
       </c>
       <c r="I515" s="5" t="n">
-        <v>23020</v>
+        <v>23070</v>
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
@@ -33513,7 +33513,7 @@
         <v>10612000</v>
       </c>
       <c r="L515" s="5" t="n">
-        <v>23020</v>
+        <v>23070</v>
       </c>
       <c r="M515" s="3" t="inlineStr">
         <is>
@@ -34106,7 +34106,7 @@
         </is>
       </c>
       <c r="E525" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F525" s="3" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>10565000</v>
       </c>
       <c r="I525" s="5" t="n">
-        <v>22918</v>
+        <v>22967</v>
       </c>
       <c r="J525" s="3" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>10565000</v>
       </c>
       <c r="L525" s="5" t="n">
-        <v>22918</v>
+        <v>22967</v>
       </c>
       <c r="M525" s="3" t="inlineStr">
         <is>
@@ -34354,7 +34354,7 @@
         </is>
       </c>
       <c r="E529" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F529" s="3" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>11415000</v>
       </c>
       <c r="I529" s="5" t="n">
-        <v>24443</v>
+        <v>24391</v>
       </c>
       <c r="J529" s="3" t="inlineStr">
         <is>
@@ -34381,7 +34381,7 @@
         <v>11415000</v>
       </c>
       <c r="L529" s="5" t="n">
-        <v>24443</v>
+        <v>24391</v>
       </c>
       <c r="M529" s="3" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         </is>
       </c>
       <c r="E532" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F532" s="3" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>7984000</v>
       </c>
       <c r="I532" s="5" t="n">
-        <v>25266</v>
+        <v>25186</v>
       </c>
       <c r="J532" s="3" t="inlineStr">
         <is>
@@ -34567,7 +34567,7 @@
         <v>7984000</v>
       </c>
       <c r="L532" s="5" t="n">
-        <v>25266</v>
+        <v>25186</v>
       </c>
       <c r="M532" s="3" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         </is>
       </c>
       <c r="E535" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F535" s="3" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>10540000</v>
       </c>
       <c r="I535" s="5" t="n">
-        <v>22863</v>
+        <v>22913</v>
       </c>
       <c r="J535" s="3" t="inlineStr">
         <is>
@@ -34753,7 +34753,7 @@
         <v>10540000</v>
       </c>
       <c r="L535" s="5" t="n">
-        <v>22863</v>
+        <v>22913</v>
       </c>
       <c r="M535" s="3" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         </is>
       </c>
       <c r="E537" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F537" s="3" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>7341000</v>
       </c>
       <c r="I537" s="5" t="n">
-        <v>23231</v>
+        <v>23158</v>
       </c>
       <c r="J537" s="3" t="inlineStr">
         <is>
@@ -34877,7 +34877,7 @@
         <v>7341000</v>
       </c>
       <c r="L537" s="5" t="n">
-        <v>23231</v>
+        <v>23158</v>
       </c>
       <c r="M537" s="3" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         </is>
       </c>
       <c r="E539" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F539" s="3" t="inlineStr">
         <is>
@@ -34990,7 +34990,7 @@
         <v>11381000</v>
       </c>
       <c r="I539" s="5" t="n">
-        <v>24370</v>
+        <v>24318</v>
       </c>
       <c r="J539" s="3" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>11381000</v>
       </c>
       <c r="L539" s="5" t="n">
-        <v>24370</v>
+        <v>24318</v>
       </c>
       <c r="M539" s="3" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="E542" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F542" s="3" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>7960000</v>
       </c>
       <c r="I542" s="5" t="n">
-        <v>25190</v>
+        <v>25110</v>
       </c>
       <c r="J542" s="3" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>7960000</v>
       </c>
       <c r="L542" s="5" t="n">
-        <v>25190</v>
+        <v>25110</v>
       </c>
       <c r="M542" s="3" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         </is>
       </c>
       <c r="E545" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F545" s="3" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>10515000</v>
       </c>
       <c r="I545" s="5" t="n">
-        <v>22809</v>
+        <v>22859</v>
       </c>
       <c r="J545" s="3" t="inlineStr">
         <is>
@@ -35373,7 +35373,7 @@
         <v>10515000</v>
       </c>
       <c r="L545" s="5" t="n">
-        <v>22809</v>
+        <v>22859</v>
       </c>
       <c r="M545" s="3" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         </is>
       </c>
       <c r="E549" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F549" s="3" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>11346000</v>
       </c>
       <c r="I549" s="5" t="n">
-        <v>24296</v>
+        <v>24244</v>
       </c>
       <c r="J549" s="3" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>11346000</v>
       </c>
       <c r="L549" s="5" t="n">
-        <v>24296</v>
+        <v>24244</v>
       </c>
       <c r="M549" s="3" t="inlineStr">
         <is>
@@ -35780,7 +35780,7 @@
         </is>
       </c>
       <c r="E552" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F552" s="3" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>7936000</v>
       </c>
       <c r="I552" s="5" t="n">
-        <v>25114</v>
+        <v>25035</v>
       </c>
       <c r="J552" s="3" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>7936000</v>
       </c>
       <c r="L552" s="5" t="n">
-        <v>25114</v>
+        <v>25035</v>
       </c>
       <c r="M552" s="3" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         </is>
       </c>
       <c r="E555" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F555" s="3" t="inlineStr">
         <is>
@@ -35982,7 +35982,7 @@
         <v>10361000</v>
       </c>
       <c r="I555" s="5" t="n">
-        <v>22475</v>
+        <v>22524</v>
       </c>
       <c r="J555" s="3" t="inlineStr">
         <is>
@@ -35993,7 +35993,7 @@
         <v>10361000</v>
       </c>
       <c r="L555" s="5" t="n">
-        <v>22475</v>
+        <v>22524</v>
       </c>
       <c r="M555" s="3" t="inlineStr">
         <is>
@@ -36214,7 +36214,7 @@
         </is>
       </c>
       <c r="E559" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F559" s="3" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>11634000</v>
       </c>
       <c r="I559" s="5" t="n">
-        <v>24912</v>
+        <v>24859</v>
       </c>
       <c r="J559" s="3" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>11634000</v>
       </c>
       <c r="L559" s="5" t="n">
-        <v>24912</v>
+        <v>24859</v>
       </c>
       <c r="M559" s="3" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         </is>
       </c>
       <c r="E565" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F565" s="3" t="inlineStr">
         <is>
@@ -36602,7 +36602,7 @@
         <v>10330000</v>
       </c>
       <c r="I565" s="5" t="n">
-        <v>22408</v>
+        <v>22457</v>
       </c>
       <c r="J565" s="3" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>10330000</v>
       </c>
       <c r="L565" s="5" t="n">
-        <v>22408</v>
+        <v>22457</v>
       </c>
       <c r="M565" s="3" t="inlineStr">
         <is>
@@ -37020,7 +37020,7 @@
         </is>
       </c>
       <c r="E572" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F572" s="3" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>7671000</v>
       </c>
       <c r="I572" s="5" t="n">
-        <v>24275</v>
+        <v>24199</v>
       </c>
       <c r="J572" s="3" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>7671000</v>
       </c>
       <c r="L572" s="5" t="n">
-        <v>24275</v>
+        <v>24199</v>
       </c>
       <c r="M572" s="3" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         </is>
       </c>
       <c r="E575" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F575" s="3" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>10299000</v>
       </c>
       <c r="I575" s="5" t="n">
-        <v>22341</v>
+        <v>22389</v>
       </c>
       <c r="J575" s="3" t="inlineStr">
         <is>
@@ -37233,7 +37233,7 @@
         <v>10299000</v>
       </c>
       <c r="L575" s="5" t="n">
-        <v>22341</v>
+        <v>22389</v>
       </c>
       <c r="M575" s="3" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         </is>
       </c>
       <c r="E577" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F577" s="3" t="inlineStr">
         <is>
@@ -37346,7 +37346,7 @@
         <v>7253000</v>
       </c>
       <c r="I577" s="5" t="n">
-        <v>22953</v>
+        <v>22880</v>
       </c>
       <c r="J577" s="3" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>7253000</v>
       </c>
       <c r="L577" s="5" t="n">
-        <v>22953</v>
+        <v>22880</v>
       </c>
       <c r="M577" s="3" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         </is>
       </c>
       <c r="E579" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F579" s="3" t="inlineStr">
         <is>
@@ -37470,7 +37470,7 @@
         <v>11245000</v>
       </c>
       <c r="I579" s="5" t="n">
-        <v>24079</v>
+        <v>24028</v>
       </c>
       <c r="J579" s="3" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>11245000</v>
       </c>
       <c r="L579" s="5" t="n">
-        <v>24079</v>
+        <v>24028</v>
       </c>
       <c r="M579" s="3" t="inlineStr">
         <is>
@@ -37640,7 +37640,7 @@
         </is>
       </c>
       <c r="E582" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F582" s="3" t="inlineStr">
         <is>
@@ -37656,7 +37656,7 @@
         <v>7648000</v>
       </c>
       <c r="I582" s="5" t="n">
-        <v>24203</v>
+        <v>24126</v>
       </c>
       <c r="J582" s="3" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>7648000</v>
       </c>
       <c r="L582" s="5" t="n">
-        <v>24203</v>
+        <v>24126</v>
       </c>
       <c r="M582" s="3" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         </is>
       </c>
       <c r="E585" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F585" s="3" t="inlineStr">
         <is>
@@ -37842,7 +37842,7 @@
         <v>10268000</v>
       </c>
       <c r="I585" s="5" t="n">
-        <v>22273</v>
+        <v>22322</v>
       </c>
       <c r="J585" s="3" t="inlineStr">
         <is>
@@ -37853,7 +37853,7 @@
         <v>10268000</v>
       </c>
       <c r="L585" s="5" t="n">
-        <v>22273</v>
+        <v>22322</v>
       </c>
       <c r="M585" s="3" t="inlineStr">
         <is>
@@ -38074,7 +38074,7 @@
         </is>
       </c>
       <c r="E589" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F589" s="3" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>11530000</v>
       </c>
       <c r="I589" s="5" t="n">
-        <v>24690</v>
+        <v>24637</v>
       </c>
       <c r="J589" s="3" t="inlineStr">
         <is>
@@ -38101,7 +38101,7 @@
         <v>11530000</v>
       </c>
       <c r="L589" s="5" t="n">
-        <v>24690</v>
+        <v>24637</v>
       </c>
       <c r="M589" s="3" t="inlineStr">
         <is>
@@ -38446,7 +38446,7 @@
         </is>
       </c>
       <c r="E595" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F595" s="3" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>10238000</v>
       </c>
       <c r="I595" s="5" t="n">
-        <v>22208</v>
+        <v>22257</v>
       </c>
       <c r="J595" s="3" t="inlineStr">
         <is>
@@ -38473,7 +38473,7 @@
         <v>10238000</v>
       </c>
       <c r="L595" s="5" t="n">
-        <v>22208</v>
+        <v>22257</v>
       </c>
       <c r="M595" s="3" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         </is>
       </c>
       <c r="E599" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F599" s="3" t="inlineStr">
         <is>
@@ -38710,7 +38710,7 @@
         <v>11496000</v>
       </c>
       <c r="I599" s="5" t="n">
-        <v>24617</v>
+        <v>24564</v>
       </c>
       <c r="J599" s="3" t="inlineStr">
         <is>
@@ -38721,7 +38721,7 @@
         <v>11496000</v>
       </c>
       <c r="L599" s="5" t="n">
-        <v>24617</v>
+        <v>24564</v>
       </c>
       <c r="M599" s="3" t="inlineStr">
         <is>
@@ -38880,7 +38880,7 @@
         </is>
       </c>
       <c r="E602" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F602" s="3" t="inlineStr">
         <is>
@@ -38896,7 +38896,7 @@
         <v>7579000</v>
       </c>
       <c r="I602" s="5" t="n">
-        <v>23984</v>
+        <v>23909</v>
       </c>
       <c r="J602" s="3" t="inlineStr">
         <is>
@@ -38907,7 +38907,7 @@
         <v>7579000</v>
       </c>
       <c r="L602" s="5" t="n">
-        <v>23984</v>
+        <v>23909</v>
       </c>
       <c r="M602" s="3" t="inlineStr">
         <is>
@@ -39066,7 +39066,7 @@
         </is>
       </c>
       <c r="E605" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F605" s="3" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>10177000</v>
       </c>
       <c r="I605" s="5" t="n">
-        <v>22076</v>
+        <v>22124</v>
       </c>
       <c r="J605" s="3" t="inlineStr">
         <is>
@@ -39093,7 +39093,7 @@
         <v>10177000</v>
       </c>
       <c r="L605" s="5" t="n">
-        <v>22076</v>
+        <v>22124</v>
       </c>
       <c r="M605" s="3" t="inlineStr">
         <is>
@@ -39500,7 +39500,7 @@
         </is>
       </c>
       <c r="E612" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F612" s="3" t="inlineStr">
         <is>
@@ -39516,7 +39516,7 @@
         <v>7557000</v>
       </c>
       <c r="I612" s="5" t="n">
-        <v>23915</v>
+        <v>23839</v>
       </c>
       <c r="J612" s="3" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>7557000</v>
       </c>
       <c r="L612" s="5" t="n">
-        <v>23915</v>
+        <v>23839</v>
       </c>
       <c r="M612" s="3" t="inlineStr">
         <is>
@@ -39686,7 +39686,7 @@
         </is>
       </c>
       <c r="E615" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F615" s="3" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>10146000</v>
       </c>
       <c r="I615" s="5" t="n">
-        <v>22009</v>
+        <v>22057</v>
       </c>
       <c r="J615" s="3" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>10146000</v>
       </c>
       <c r="L615" s="5" t="n">
-        <v>22009</v>
+        <v>22057</v>
       </c>
       <c r="M615" s="3" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         </is>
       </c>
       <c r="E619" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F619" s="3" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>11078000</v>
       </c>
       <c r="I619" s="5" t="n">
-        <v>23722</v>
+        <v>23671</v>
       </c>
       <c r="J619" s="3" t="inlineStr">
         <is>
@@ -39961,7 +39961,7 @@
         <v>11078000</v>
       </c>
       <c r="L619" s="5" t="n">
-        <v>23722</v>
+        <v>23671</v>
       </c>
       <c r="M619" s="3" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         </is>
       </c>
       <c r="E622" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F622" s="3" t="inlineStr">
         <is>
@@ -40136,7 +40136,7 @@
         <v>7534000</v>
       </c>
       <c r="I622" s="5" t="n">
-        <v>23842</v>
+        <v>23767</v>
       </c>
       <c r="J622" s="3" t="inlineStr">
         <is>
@@ -40147,7 +40147,7 @@
         <v>7534000</v>
       </c>
       <c r="L622" s="5" t="n">
-        <v>23842</v>
+        <v>23767</v>
       </c>
       <c r="M622" s="3" t="inlineStr">
         <is>
@@ -40306,7 +40306,7 @@
         </is>
       </c>
       <c r="E625" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F625" s="3" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>10116000</v>
       </c>
       <c r="I625" s="5" t="n">
-        <v>21944</v>
+        <v>21991</v>
       </c>
       <c r="J625" s="3" t="inlineStr">
         <is>
@@ -40333,7 +40333,7 @@
         <v>10116000</v>
       </c>
       <c r="L625" s="5" t="n">
-        <v>21944</v>
+        <v>21991</v>
       </c>
       <c r="M625" s="3" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         </is>
       </c>
       <c r="E629" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F629" s="3" t="inlineStr">
         <is>
@@ -40570,7 +40570,7 @@
         <v>11044000</v>
       </c>
       <c r="I629" s="5" t="n">
-        <v>23649</v>
+        <v>23598</v>
       </c>
       <c r="J629" s="3" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>11044000</v>
       </c>
       <c r="L629" s="5" t="n">
-        <v>23649</v>
+        <v>23598</v>
       </c>
       <c r="M629" s="3" t="inlineStr">
         <is>
@@ -40740,7 +40740,7 @@
         </is>
       </c>
       <c r="E632" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F632" s="3" t="inlineStr">
         <is>
@@ -40756,7 +40756,7 @@
         <v>7511000</v>
       </c>
       <c r="I632" s="5" t="n">
-        <v>23769</v>
+        <v>23694</v>
       </c>
       <c r="J632" s="3" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>7511000</v>
       </c>
       <c r="L632" s="5" t="n">
-        <v>23769</v>
+        <v>23694</v>
       </c>
       <c r="M632" s="3" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         </is>
       </c>
       <c r="E635" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F635" s="3" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>10016000</v>
       </c>
       <c r="I635" s="5" t="n">
-        <v>21727</v>
+        <v>21774</v>
       </c>
       <c r="J635" s="3" t="inlineStr">
         <is>
@@ -40953,7 +40953,7 @@
         <v>10016000</v>
       </c>
       <c r="L635" s="5" t="n">
-        <v>21727</v>
+        <v>21774</v>
       </c>
       <c r="M635" s="3" t="inlineStr">
         <is>
@@ -41174,7 +41174,7 @@
         </is>
       </c>
       <c r="E639" s="4" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F639" s="3" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>11012000</v>
       </c>
       <c r="I639" s="5" t="n">
-        <v>23580</v>
+        <v>23530</v>
       </c>
       <c r="J639" s="3" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>11012000</v>
       </c>
       <c r="L639" s="5" t="n">
-        <v>23580</v>
+        <v>23530</v>
       </c>
       <c r="M639" s="3" t="inlineStr">
         <is>
@@ -41360,7 +41360,7 @@
         </is>
       </c>
       <c r="E642" s="4" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F642" s="3" t="inlineStr">
         <is>
@@ -41376,7 +41376,7 @@
         <v>7489000</v>
       </c>
       <c r="I642" s="5" t="n">
-        <v>23699</v>
+        <v>23625</v>
       </c>
       <c r="J642" s="3" t="inlineStr">
         <is>
@@ -41387,7 +41387,7 @@
         <v>7489000</v>
       </c>
       <c r="L642" s="5" t="n">
-        <v>23699</v>
+        <v>23625</v>
       </c>
       <c r="M642" s="3" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         </is>
       </c>
       <c r="E645" s="4" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F645" s="3" t="inlineStr">
         <is>
@@ -41562,7 +41562,7 @@
         <v>9724000</v>
       </c>
       <c r="I645" s="5" t="n">
-        <v>21093</v>
+        <v>21139</v>
       </c>
       <c r="J645" s="3" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>9724000</v>
       </c>
       <c r="L645" s="5" t="n">
-        <v>21093</v>
+        <v>21139</v>
       </c>
       <c r="M645" s="3" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         </is>
       </c>
       <c r="E649" s="4" t="n">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F649" s="3" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>11080000</v>
       </c>
       <c r="I649" s="5" t="n">
-        <v>25828</v>
+        <v>25767</v>
       </c>
       <c r="J649" s="3" t="inlineStr">
         <is>
@@ -41821,7 +41821,7 @@
         <v>11080000</v>
       </c>
       <c r="L649" s="5" t="n">
-        <v>25828</v>
+        <v>25767</v>
       </c>
       <c r="M649" s="3" t="inlineStr">
         <is>
@@ -42118,9 +42118,9 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1284万
-$26,480/呎
+$26,426/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -42150,9 +42150,9 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1283万
-$25,711/呎
+$25,660/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -42181,9 +42181,9 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1280万
-$26,402/呎
+$26,348/呎
 (26年-05月-06日)</t>
         </is>
       </c>
@@ -42213,9 +42213,9 @@
       </c>
       <c r="H7" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1280万
-$25,647/呎
+$25,596/呎
 (26年-06月-29日)</t>
         </is>
       </c>
@@ -42244,9 +42244,9 @@
       </c>
       <c r="D8" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1273万
-$26,245/呎
+$26,191/呎
 (25年-01月-17日)</t>
         </is>
       </c>
@@ -42276,9 +42276,9 @@
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1268万
-$25,417/呎
+$25,366/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -42307,9 +42307,9 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1269万
-$26,167/呎
+$26,113/呎
 (26年-04月-20日)</t>
         </is>
       </c>
@@ -42339,9 +42339,9 @@
       </c>
       <c r="H9" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1264万
-$25,341/呎
+$25,290/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -42370,9 +42370,9 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1265万
-$26,087/呎
+$26,033/呎
 (26年-04月-21日)</t>
         </is>
       </c>
@@ -42402,9 +42402,9 @@
       </c>
       <c r="H10" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1261万
-$25,265/呎
+$25,214/呎
 (26年-05月-12日)</t>
         </is>
       </c>
@@ -42433,9 +42433,9 @@
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1261万
-$26,008/呎
+$25,955/呎
 (25年-01月-22日)</t>
         </is>
       </c>
@@ -42465,9 +42465,9 @@
       </c>
       <c r="H11" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1264万
-$25,327/呎
+$25,276/呎
 (26年-07月-06日)</t>
         </is>
       </c>
@@ -42496,9 +42496,9 @@
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1258万
-$25,932/呎
+$25,879/呎
 (26年-04月-20日)</t>
         </is>
       </c>
@@ -42528,9 +42528,9 @@
       </c>
       <c r="H12" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1260万
-$25,261/呎
+$25,210/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -42559,9 +42559,9 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1254万
-$25,856/呎
+$25,802/呎
 (26年-04月-20日)</t>
         </is>
       </c>
@@ -42591,9 +42591,9 @@
       </c>
       <c r="H13" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1257万
-$25,196/呎
+$25,146/呎
 (26年-06月-26日)</t>
         </is>
       </c>
@@ -42622,9 +42622,9 @@
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1250万
-$25,777/呎
+$25,724/呎
 (25年-11月-26日)</t>
         </is>
       </c>
@@ -42646,17 +42646,17 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 449呎 (2房)
+          <t>F | 448呎 (2房)
 $1048万
-$23,347/呎
+$23,400/呎
 (26年-08月-06日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1246万
-$24,966/呎
+$24,916/呎
 (26年-05月-07日)</t>
         </is>
       </c>
@@ -42685,9 +42685,9 @@
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1246万
-$25,701/呎
+$25,648/呎
 (24年-07月-18日)</t>
         </is>
       </c>
@@ -42709,17 +42709,17 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 449呎 (2房)
+          <t>F | 448呎 (2房)
 $1045万
-$23,278/呎
+$23,330/呎
 (26年-08月-28日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1242万
-$24,890/呎
+$24,840/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -42772,17 +42772,17 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 449呎 (2房)
+          <t>F | 448呎 (2房)
 $1042万
-$23,209/呎
+$23,261/呎
 (26年-10月-18日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1238万
-$24,816/呎
+$24,766/呎
 (26年-06月-10日)</t>
         </is>
       </c>
@@ -42811,9 +42811,9 @@
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1235万
-$25,470/呎
+$25,418/呎
 (25年-09月-10日)</t>
         </is>
       </c>
@@ -42843,9 +42843,9 @@
       </c>
       <c r="H17" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1231万
-$24,667/呎
+$24,618/呎
 (26年-05月-19日)</t>
         </is>
       </c>
@@ -42874,9 +42874,9 @@
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1232万
-$25,394/呎
+$25,342/呎
 (24年-10月-30日)</t>
         </is>
       </c>
@@ -42906,9 +42906,9 @@
       </c>
       <c r="H18" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1227万
-$24,593/呎
+$24,544/呎
 (26年-04月-30日)</t>
         </is>
       </c>
@@ -42937,9 +42937,9 @@
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1228万
-$25,318/呎
+$25,265/呎
 (25年-01月-06日)</t>
         </is>
       </c>
@@ -42961,17 +42961,17 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 449呎 (2房)
+          <t>F | 448呎 (2房)
 $1030万
-$22,933/呎
+$22,984/呎
 (26年-09月-09日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1224万
-$24,521/呎
+$24,472/呎
 (26年-05月-20日)</t>
         </is>
       </c>
@@ -43000,9 +43000,9 @@
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1224万
-$25,243/呎
+$25,191/呎
 (24年-10月-29日)</t>
         </is>
       </c>
@@ -43024,17 +43024,17 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 449呎 (2房)
+          <t>F | 448呎 (2房)
 $1027万
-$22,864/呎
+$22,915/呎
 (26年-09月-04日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1234万
-$24,727/呎
+$24,678/呎
 (26年-06月-30日)</t>
         </is>
       </c>
@@ -43063,9 +43063,9 @@
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1221万
-$25,167/呎
+$25,115/呎
 (25年-06月-25日)</t>
         </is>
       </c>
@@ -43095,9 +43095,9 @@
       </c>
       <c r="H21" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1231万
-$24,667/呎
+$24,618/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -43158,9 +43158,9 @@
       </c>
       <c r="H22" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1213万
-$24,301/呎
+$24,252/呎
 (26年-05月-22日)</t>
         </is>
       </c>
@@ -43189,9 +43189,9 @@
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1213万
-$25,016/呎
+$24,965/呎
 (24年-07月-02日)</t>
         </is>
       </c>
@@ -43221,9 +43221,9 @@
       </c>
       <c r="H23" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1209万
-$24,228/呎
+$24,180/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -43252,9 +43252,9 @@
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1210万
-$24,942/呎
+$24,891/呎
 (24年-06月-26日)</t>
         </is>
       </c>
@@ -43284,9 +43284,9 @@
       </c>
       <c r="H24" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1205万
-$24,156/呎
+$24,108/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -43315,9 +43315,9 @@
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1202万
-$24,794/呎
+$24,743/呎
 (25年-03月-06日)</t>
         </is>
       </c>
@@ -43347,9 +43347,9 @@
       </c>
       <c r="H25" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1218万
-$24,407/呎
+$24,358/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -43378,9 +43378,9 @@
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1199万
-$24,720/呎
+$24,669/呎
 (25年-07月-24日)</t>
         </is>
       </c>
@@ -43410,9 +43410,9 @@
       </c>
       <c r="H26" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1215万
-$24,349/呎
+$24,300/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -43441,9 +43441,9 @@
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1195万
-$24,645/呎
+$24,595/呎
 (25年-07月-28日)</t>
         </is>
       </c>
@@ -43473,9 +43473,9 @@
       </c>
       <c r="H27" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1212万
-$24,291/呎
+$24,242/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -43504,9 +43504,9 @@
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1192万
-$24,571/呎
+$24,521/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -43536,9 +43536,9 @@
       </c>
       <c r="H28" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1209万
-$24,230/呎
+$24,182/呎
 (26年-07月-17日)</t>
         </is>
       </c>
@@ -43567,9 +43567,9 @@
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>C | 485呎 (2房)
+          <t>C | 486呎 (2房)
 $1188万
-$24,497/呎
+$24,447/呎
 (26年-05月-28日)</t>
         </is>
       </c>
@@ -43599,9 +43599,9 @@
       </c>
       <c r="H29" s="20" t="inlineStr">
         <is>
-          <t>G | 499呎 (2房)
+          <t>G | 500呎 (2房)
 $1206万
-$24,172/呎
+$24,124/呎
 (26年-07月-29日)</t>
         </is>
       </c>
@@ -45812,7 +45812,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -45822,7 +45822,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>214</t>
+          <t>215</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -45941,9 +45941,9 @@
       </c>
       <c r="G5" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1090万
-$23,644/呎
+$23,696/呎
 (26年-06月-26日)</t>
         </is>
       </c>
@@ -45965,9 +45965,9 @@
       </c>
       <c r="J5" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $812万
-$25,693/呎
+$25,612/呎
 (26年-07月-06日)</t>
         </is>
       </c>
@@ -45996,9 +45996,9 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1191万
-$25,501/呎
+$25,447/呎
 (26年-09月-15日)</t>
         </is>
       </c>
@@ -46028,9 +46028,9 @@
       </c>
       <c r="G6" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1087万
-$23,588/呎
+$23,639/呎
 (26年-06月-26日)</t>
         </is>
       </c>
@@ -46052,18 +46052,18 @@
       </c>
       <c r="J6" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $810万
-$25,620/呎
+$25,539/呎
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="20" t="inlineStr">
         <is>
           <t>K | 329呎 (1房)
-$967万
-$29,401/呎
-(在售)</t>
+$851万
+$25,875/呎
+(26年-10月-28日)</t>
         </is>
       </c>
     </row>
@@ -46083,9 +46083,9 @@
       </c>
       <c r="C7" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1183万
-$25,336/呎
+$25,282/呎
 (25年-09月-26日)</t>
         </is>
       </c>
@@ -46115,9 +46115,9 @@
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1085万
-$23,544/呎
+$23,596/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -46139,9 +46139,9 @@
       </c>
       <c r="J7" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $807万
-$25,541/呎
+$25,461/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -46170,9 +46170,9 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1176万
-$25,186/呎
+$25,132/呎
 (24年-10月-22日)</t>
         </is>
       </c>
@@ -46202,9 +46202,9 @@
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1081万
-$23,443/呎
+$23,493/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -46226,9 +46226,9 @@
       </c>
       <c r="J8" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $802万
-$25,389/呎
+$25,309/呎
 (26年-04月-22日)</t>
         </is>
       </c>
@@ -46257,9 +46257,9 @@
       </c>
       <c r="C9" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1173万
-$25,109/呎
+$25,056/呎
 (24年-08月-20日)</t>
         </is>
       </c>
@@ -46289,9 +46289,9 @@
       </c>
       <c r="G9" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1078万
-$23,386/呎
+$23,437/呎
 (26年-07月-03日)</t>
         </is>
       </c>
@@ -46313,9 +46313,9 @@
       </c>
       <c r="J9" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $800万
-$25,313/呎
+$25,233/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -46344,9 +46344,9 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1169万
-$25,034/呎
+$24,981/呎
 (25年-01月-21日)</t>
         </is>
       </c>
@@ -46376,9 +46376,9 @@
       </c>
       <c r="G10" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1076万
-$23,330/呎
+$23,380/呎
 (26年-07月-02日)</t>
         </is>
       </c>
@@ -46400,9 +46400,9 @@
       </c>
       <c r="J10" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $798万
-$25,237/呎
+$25,158/呎
 (26年-05月-04日)</t>
         </is>
       </c>
@@ -46431,9 +46431,9 @@
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1166万
-$24,959/呎
+$24,906/呎
 (26年-04月-21日)</t>
         </is>
       </c>
@@ -46463,9 +46463,9 @@
       </c>
       <c r="G11" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1073万
-$23,273/呎
+$23,324/呎
 (26年-07月-08日)</t>
         </is>
       </c>
@@ -46487,9 +46487,9 @@
       </c>
       <c r="J11" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $795万
-$25,161/呎
+$25,082/呎
 (24年-08月-02日)</t>
         </is>
       </c>
@@ -46518,9 +46518,9 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1195万
-$25,593/呎
+$25,538/呎
 (22年-09月-30日)</t>
         </is>
       </c>
@@ -46550,9 +46550,9 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1070万
-$23,219/呎
+$23,270/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -46574,9 +46574,9 @@
       </c>
       <c r="J12" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $793万
-$25,089/呎
+$25,009/呎
 (24年-11月-13日)</t>
         </is>
       </c>
@@ -46637,9 +46637,9 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1068万
-$23,163/呎
+$23,213/呎
 (26年-07月-08日)</t>
         </is>
       </c>
@@ -46724,9 +46724,9 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1065万
-$23,106/呎
+$23,157/呎
 (26年-07月-13日)</t>
         </is>
       </c>
@@ -46779,9 +46779,9 @@
       </c>
       <c r="C15" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1152万
-$24,664/呎
+$24,611/呎
 (24年-06月-06日)</t>
         </is>
       </c>
@@ -46811,9 +46811,9 @@
       </c>
       <c r="G15" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1063万
-$23,052/呎
+$23,102/呎
 (26年-07月-09日)</t>
         </is>
       </c>
@@ -46898,9 +46898,9 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1061万
-$23,020/呎
+$23,070/呎
 (26年-07月-07日)</t>
         </is>
       </c>
@@ -46953,9 +46953,9 @@
       </c>
       <c r="C17" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1142万
-$24,443/呎
+$24,391/呎
 (24年-06月-17日)</t>
         </is>
       </c>
@@ -46985,9 +46985,9 @@
       </c>
       <c r="G17" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1056万
-$22,918/呎
+$22,967/呎
 (26年-07月-14日)</t>
         </is>
       </c>
@@ -47040,9 +47040,9 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1138万
-$24,370/呎
+$24,318/呎
 (26年-06月-04日)</t>
         </is>
       </c>
@@ -47056,9 +47056,9 @@
       </c>
       <c r="E18" s="20" t="inlineStr">
         <is>
-          <t>D | 316呎 (1房)
+          <t>D | 317呎 (1房)
 $734万
-$23,231/呎
+$23,158/呎
 (26年-09月-16日)</t>
         </is>
       </c>
@@ -47072,9 +47072,9 @@
       </c>
       <c r="G18" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1054万
-$22,863/呎
+$22,913/呎
 (26年-06月-30日)</t>
         </is>
       </c>
@@ -47096,9 +47096,9 @@
       </c>
       <c r="J18" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $798万
-$25,266/呎
+$25,186/呎
 (22年-09月-29日)</t>
         </is>
       </c>
@@ -47127,9 +47127,9 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1135万
-$24,296/呎
+$24,244/呎
 (26年-06月-12日)</t>
         </is>
       </c>
@@ -47159,9 +47159,9 @@
       </c>
       <c r="G19" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1052万
-$22,809/呎
+$22,859/呎
 (26年-06月-30日)</t>
         </is>
       </c>
@@ -47183,9 +47183,9 @@
       </c>
       <c r="J19" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $796万
-$25,190/呎
+$25,110/呎
 (22年-09月-29日)</t>
         </is>
       </c>
@@ -47214,9 +47214,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1163万
-$24,912/呎
+$24,859/呎
 (22年-09月-30日)</t>
         </is>
       </c>
@@ -47246,9 +47246,9 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1036万
-$22,475/呎
+$22,524/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -47270,9 +47270,9 @@
       </c>
       <c r="J20" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $794万
-$25,114/呎
+$25,035/呎
 (22年-09月-26日)</t>
         </is>
       </c>
@@ -47333,9 +47333,9 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1033万
-$22,408/呎
+$22,457/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -47388,9 +47388,9 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1124万
-$24,079/呎
+$24,028/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -47404,9 +47404,9 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>D | 316呎 (1房)
+          <t>D | 317呎 (1房)
 $725万
-$22,953/呎
+$22,880/呎
 (26年-08月-28日)</t>
         </is>
       </c>
@@ -47420,9 +47420,9 @@
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1030万
-$22,341/呎
+$22,389/呎
 (26年-06月-09日)</t>
         </is>
       </c>
@@ -47444,9 +47444,9 @@
       </c>
       <c r="J22" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $767万
-$24,275/呎
+$24,199/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -47475,9 +47475,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1153万
-$24,690/呎
+$24,637/呎
 (22年-10月-11日)</t>
         </is>
       </c>
@@ -47507,9 +47507,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1027万
-$22,273/呎
+$22,322/呎
 (26年-06月-11日)</t>
         </is>
       </c>
@@ -47531,9 +47531,9 @@
       </c>
       <c r="J23" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $765万
-$24,203/呎
+$24,126/呎
 (22年-09月-26日)</t>
         </is>
       </c>
@@ -47562,9 +47562,9 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1150万
-$24,617/呎
+$24,564/呎
 (22年-10月-05日)</t>
         </is>
       </c>
@@ -47594,9 +47594,9 @@
       </c>
       <c r="G24" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1024万
-$22,208/呎
+$22,257/呎
 (26年-06月-29日)</t>
         </is>
       </c>
@@ -47681,9 +47681,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1018万
-$22,076/呎
+$22,124/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -47705,9 +47705,9 @@
       </c>
       <c r="J25" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $758万
-$23,984/呎
+$23,909/呎
 (24年-07月-02日)</t>
         </is>
       </c>
@@ -47736,9 +47736,9 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1108万
-$23,722/呎
+$23,671/呎
 (24年-07月-29日)</t>
         </is>
       </c>
@@ -47768,9 +47768,9 @@
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1015万
-$22,009/呎
+$22,057/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -47792,9 +47792,9 @@
       </c>
       <c r="J26" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $756万
-$23,915/呎
+$23,839/呎
 (24年-05月-30日)</t>
         </is>
       </c>
@@ -47823,9 +47823,9 @@
       </c>
       <c r="C27" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1104万
-$23,649/呎
+$23,598/呎
 (26年-04月-21日)</t>
         </is>
       </c>
@@ -47855,9 +47855,9 @@
       </c>
       <c r="G27" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1012万
-$21,944/呎
+$21,991/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -47879,9 +47879,9 @@
       </c>
       <c r="J27" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $753万
-$23,842/呎
+$23,767/呎
 (24年-05月-27日)</t>
         </is>
       </c>
@@ -47910,9 +47910,9 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>B | 467呎 (2房)
+          <t>B | 468呎 (2房)
 $1101万
-$23,580/呎
+$23,530/呎
 (26年-05月-08日)</t>
         </is>
       </c>
@@ -47942,9 +47942,9 @@
       </c>
       <c r="G28" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $1002万
-$21,727/呎
+$21,774/呎
 (26年-06月-25日)</t>
         </is>
       </c>
@@ -47966,9 +47966,9 @@
       </c>
       <c r="J28" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $751万
-$23,769/呎
+$23,694/呎
 (24年-06月-05日)</t>
         </is>
       </c>
@@ -47997,9 +47997,9 @@
       </c>
       <c r="C29" s="20" t="inlineStr">
         <is>
-          <t>B | 429呎 (2房)
+          <t>B | 430呎 (2房)
 $1108万
-$25,828/呎
+$25,767/呎
 (26年-06月-16日)</t>
         </is>
       </c>
@@ -48029,9 +48029,9 @@
       </c>
       <c r="G29" s="20" t="inlineStr">
         <is>
-          <t>F | 461呎 (2房)
+          <t>F | 460呎 (2房)
 $972万
-$21,093/呎
+$21,139/呎
 (26年-06月-22日)</t>
         </is>
       </c>
@@ -48053,9 +48053,9 @@
       </c>
       <c r="J29" s="20" t="inlineStr">
         <is>
-          <t>J | 316呎 (1房)
+          <t>J | 317呎 (1房)
 $749万
-$23,699/呎
+$23,625/呎
 (24年-11月-05日)</t>
         </is>
       </c>
